--- a/data/nzd0560/nzd0560.xlsx
+++ b/data/nzd0560/nzd0560.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH267"/>
+  <dimension ref="A1:AH269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29090,7 +29090,7 @@
         <v>291.48</v>
       </c>
       <c r="D267" t="n">
-        <v>279.81</v>
+        <v>291.21</v>
       </c>
       <c r="E267" t="n">
         <v>305.99</v>
@@ -29105,16 +29105,16 @@
         <v>256.27</v>
       </c>
       <c r="I267" t="n">
-        <v>332.87</v>
+        <v>287.21</v>
       </c>
       <c r="J267" t="n">
-        <v>325.49</v>
+        <v>296.87</v>
       </c>
       <c r="K267" t="n">
-        <v>325.63</v>
+        <v>300.75</v>
       </c>
       <c r="L267" t="n">
-        <v>322.45</v>
+        <v>305.71</v>
       </c>
       <c r="M267" t="n">
         <v>280.22</v>
@@ -29144,13 +29144,13 @@
         <v>311.17</v>
       </c>
       <c r="V267" t="n">
-        <v>333.08</v>
+        <v>320.99</v>
       </c>
       <c r="W267" t="n">
-        <v>340.63</v>
+        <v>327.61</v>
       </c>
       <c r="X267" t="n">
-        <v>337.53</v>
+        <v>328.44</v>
       </c>
       <c r="Y267" t="n">
         <v>317.52</v>
@@ -29162,10 +29162,10 @@
         <v>337.12</v>
       </c>
       <c r="AB267" t="n">
-        <v>362.87</v>
+        <v>354.1</v>
       </c>
       <c r="AC267" t="n">
-        <v>371.38</v>
+        <v>362.66</v>
       </c>
       <c r="AD267" t="n">
         <v>362.02</v>
@@ -29182,6 +29182,222 @@
       <c r="AH267" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:21:03+00:00</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>294.23</v>
+      </c>
+      <c r="C268" t="n">
+        <v>291.23</v>
+      </c>
+      <c r="D268" t="n">
+        <v>291.26</v>
+      </c>
+      <c r="E268" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="F268" t="n">
+        <v>304.74</v>
+      </c>
+      <c r="G268" t="n">
+        <v>293.23</v>
+      </c>
+      <c r="H268" t="n">
+        <v>255.48</v>
+      </c>
+      <c r="I268" t="n">
+        <v>276.15</v>
+      </c>
+      <c r="J268" t="n">
+        <v>279.62</v>
+      </c>
+      <c r="K268" t="n">
+        <v>287.49</v>
+      </c>
+      <c r="L268" t="n">
+        <v>296.94</v>
+      </c>
+      <c r="M268" t="n">
+        <v>273.25</v>
+      </c>
+      <c r="N268" t="n">
+        <v>296.96</v>
+      </c>
+      <c r="O268" t="n">
+        <v>319.76</v>
+      </c>
+      <c r="P268" t="n">
+        <v>336.88</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>348.27</v>
+      </c>
+      <c r="R268" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="S268" t="n">
+        <v>330.18</v>
+      </c>
+      <c r="T268" t="n">
+        <v>299.8</v>
+      </c>
+      <c r="U268" t="n">
+        <v>291.73</v>
+      </c>
+      <c r="V268" t="n">
+        <v>315.14</v>
+      </c>
+      <c r="W268" t="n">
+        <v>325.35</v>
+      </c>
+      <c r="X268" t="n">
+        <v>325.52</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>314.14</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>321.48</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>330.74</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>346.39</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>356.19</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>354.3</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>348.32</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>352.86</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>383.85</v>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:21:16+00:00</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>297.57</v>
+      </c>
+      <c r="C269" t="n">
+        <v>302.02</v>
+      </c>
+      <c r="D269" t="n">
+        <v>298.02</v>
+      </c>
+      <c r="E269" t="n">
+        <v>312.53</v>
+      </c>
+      <c r="F269" t="n">
+        <v>306.37</v>
+      </c>
+      <c r="G269" t="n">
+        <v>292.06</v>
+      </c>
+      <c r="H269" t="n">
+        <v>257.31</v>
+      </c>
+      <c r="I269" t="n">
+        <v>273.29</v>
+      </c>
+      <c r="J269" t="n">
+        <v>278.88</v>
+      </c>
+      <c r="K269" t="n">
+        <v>288.6</v>
+      </c>
+      <c r="L269" t="n">
+        <v>301.68</v>
+      </c>
+      <c r="M269" t="n">
+        <v>284.22</v>
+      </c>
+      <c r="N269" t="n">
+        <v>304.28</v>
+      </c>
+      <c r="O269" t="n">
+        <v>315.7</v>
+      </c>
+      <c r="P269" t="n">
+        <v>327.51</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="R269" t="n">
+        <v>345.66</v>
+      </c>
+      <c r="S269" t="n">
+        <v>331.82</v>
+      </c>
+      <c r="T269" t="n">
+        <v>301.07</v>
+      </c>
+      <c r="U269" t="n">
+        <v>286.49</v>
+      </c>
+      <c r="V269" t="n">
+        <v>308.22</v>
+      </c>
+      <c r="W269" t="n">
+        <v>317.07</v>
+      </c>
+      <c r="X269" t="n">
+        <v>318.87</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>311.48</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>318.83</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>324.65</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>338.96</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>344.87</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>347.54</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>343.75</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>346.56</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>383.07</v>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29196,7 +29412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B272"/>
+  <dimension ref="A1:B274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31919,6 +32135,26 @@
       </c>
       <c r="B272" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>-0.62</v>
       </c>
     </row>
   </sheetData>
@@ -32087,28 +32323,28 @@
         <v>0.1765</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6991882085453378</v>
+        <v>-0.6989565406330271</v>
       </c>
       <c r="J2" t="n">
+        <v>268</v>
+      </c>
+      <c r="K2" t="n">
         <v>266</v>
       </c>
-      <c r="K2" t="n">
-        <v>264</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2264971277100408</v>
+        <v>0.2290425003020622</v>
       </c>
       <c r="M2" t="n">
-        <v>7.711536666335092</v>
+        <v>7.666159691017019</v>
       </c>
       <c r="N2" t="n">
-        <v>96.75555434270798</v>
+        <v>96.0497137960302</v>
       </c>
       <c r="O2" t="n">
-        <v>9.83644012550821</v>
+        <v>9.800495589307216</v>
       </c>
       <c r="P2" t="n">
-        <v>314.1744250061712</v>
+        <v>314.1720496788852</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32165,28 +32401,28 @@
         <v>0.0501</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.302918743029389</v>
+        <v>-1.306154626083272</v>
       </c>
       <c r="J3" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K3" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3353753566736377</v>
+        <v>0.339604838688592</v>
       </c>
       <c r="M3" t="n">
-        <v>10.90573726291097</v>
+        <v>10.86216754303981</v>
       </c>
       <c r="N3" t="n">
-        <v>197.1634060115314</v>
+        <v>195.9471879959247</v>
       </c>
       <c r="O3" t="n">
-        <v>14.04148873914484</v>
+        <v>13.99811372992536</v>
       </c>
       <c r="P3" t="n">
-        <v>333.3343313118967</v>
+        <v>333.3667843774608</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32243,28 +32479,28 @@
         <v>0.0344</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.062182138076115</v>
+        <v>-1.055134651188524</v>
       </c>
       <c r="J4" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K4" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L4" t="n">
-        <v>0.253715722392593</v>
+        <v>0.254895915910086</v>
       </c>
       <c r="M4" t="n">
-        <v>10.90370449561862</v>
+        <v>10.80775329183422</v>
       </c>
       <c r="N4" t="n">
-        <v>191.5721179405008</v>
+        <v>189.3557245474742</v>
       </c>
       <c r="O4" t="n">
-        <v>13.84095798492651</v>
+        <v>13.76065857971464</v>
       </c>
       <c r="P4" t="n">
-        <v>323.2314029473313</v>
+        <v>323.1605938094593</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32321,28 +32557,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.785655545710391</v>
+        <v>-0.7589559702503681</v>
       </c>
       <c r="J5" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K5" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2094162503379962</v>
+        <v>0.1973895871533272</v>
       </c>
       <c r="M5" t="n">
-        <v>9.437277015889007</v>
+        <v>9.489353351497106</v>
       </c>
       <c r="N5" t="n">
-        <v>135.3514348091132</v>
+        <v>137.1109729375301</v>
       </c>
       <c r="O5" t="n">
-        <v>11.63406355531519</v>
+        <v>11.70943948007461</v>
       </c>
       <c r="P5" t="n">
-        <v>310.8922963658041</v>
+        <v>310.6221305894932</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32399,28 +32635,28 @@
         <v>0.0596</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6813008259336967</v>
+        <v>-0.6638589709192545</v>
       </c>
       <c r="J6" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K6" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1912739400416269</v>
+        <v>0.1841474068175816</v>
       </c>
       <c r="M6" t="n">
-        <v>8.790429162708094</v>
+        <v>8.80036238628464</v>
       </c>
       <c r="N6" t="n">
-        <v>114.7779337192794</v>
+        <v>115.0881480532581</v>
       </c>
       <c r="O6" t="n">
-        <v>10.7134463978348</v>
+        <v>10.72791443167115</v>
       </c>
       <c r="P6" t="n">
-        <v>310.8971742577664</v>
+        <v>310.7217726121958</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32477,28 +32713,28 @@
         <v>0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5952393547412616</v>
+        <v>-0.5885805980158175</v>
       </c>
       <c r="J7" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K7" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L7" t="n">
-        <v>0.156357141028057</v>
+        <v>0.1552492578416703</v>
       </c>
       <c r="M7" t="n">
-        <v>8.02265137745635</v>
+        <v>7.991836430501077</v>
       </c>
       <c r="N7" t="n">
-        <v>112.4772036982088</v>
+        <v>111.7949551536987</v>
       </c>
       <c r="O7" t="n">
-        <v>10.60552703538154</v>
+        <v>10.5733133479387</v>
       </c>
       <c r="P7" t="n">
-        <v>303.5918715644058</v>
+        <v>303.5253122420101</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32555,28 +32791,28 @@
         <v>0.0326</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7601329663172809</v>
+        <v>-0.7843065138130018</v>
       </c>
       <c r="J8" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K8" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1066616523459815</v>
+        <v>0.1135681869263035</v>
       </c>
       <c r="M8" t="n">
-        <v>13.29292628283413</v>
+        <v>13.32435867551187</v>
       </c>
       <c r="N8" t="n">
-        <v>282.5004296054187</v>
+        <v>282.5300392067647</v>
       </c>
       <c r="O8" t="n">
-        <v>16.80774909395719</v>
+        <v>16.80862990272452</v>
       </c>
       <c r="P8" t="n">
-        <v>293.5394966527565</v>
+        <v>293.7829500069577</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32633,28 +32869,28 @@
         <v>0.0309</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2991577929538</v>
+        <v>-1.310875920257863</v>
       </c>
       <c r="J9" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K9" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1683064987844167</v>
+        <v>0.1780500403619499</v>
       </c>
       <c r="M9" t="n">
-        <v>16.83314185279186</v>
+        <v>16.64379030153808</v>
       </c>
       <c r="N9" t="n">
-        <v>471.0720790860059</v>
+        <v>451.698966449717</v>
       </c>
       <c r="O9" t="n">
-        <v>21.70419496516758</v>
+        <v>21.25321073272735</v>
       </c>
       <c r="P9" t="n">
-        <v>294.6914466530434</v>
+        <v>294.8089224448641</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32711,28 +32947,28 @@
         <v>0.0409</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2732431353293775</v>
+        <v>-0.2998580208378083</v>
       </c>
       <c r="J10" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K10" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01049348163632235</v>
+        <v>0.01298081802094009</v>
       </c>
       <c r="M10" t="n">
-        <v>16.51376337791501</v>
+        <v>16.33436094295222</v>
       </c>
       <c r="N10" t="n">
-        <v>413.3853890306186</v>
+        <v>404.4035680374753</v>
       </c>
       <c r="O10" t="n">
-        <v>20.33188109916588</v>
+        <v>20.10978786654587</v>
       </c>
       <c r="P10" t="n">
-        <v>291.5195652482717</v>
+        <v>291.7874869669367</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32789,28 +33025,28 @@
         <v>0.0649</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.345050309798246</v>
+        <v>-1.346197931730559</v>
       </c>
       <c r="J11" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K11" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L11" t="n">
-        <v>0.225973914782674</v>
+        <v>0.2319606822409055</v>
       </c>
       <c r="M11" t="n">
-        <v>15.02678447260779</v>
+        <v>14.90607193911281</v>
       </c>
       <c r="N11" t="n">
-        <v>364.5544146890681</v>
+        <v>355.9134360421472</v>
       </c>
       <c r="O11" t="n">
-        <v>19.09330811276736</v>
+        <v>18.86566818435401</v>
       </c>
       <c r="P11" t="n">
-        <v>312.1305371522873</v>
+        <v>312.1400823922202</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32867,28 +33103,28 @@
         <v>0.1385</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5444040422230803</v>
+        <v>-0.5566537313367739</v>
       </c>
       <c r="J12" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K12" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L12" t="n">
-        <v>0.065931891449173</v>
+        <v>0.07017246814613132</v>
       </c>
       <c r="M12" t="n">
-        <v>12.45983325999922</v>
+        <v>12.33463403080022</v>
       </c>
       <c r="N12" t="n">
-        <v>245.5616988777748</v>
+        <v>242.0130319033051</v>
       </c>
       <c r="O12" t="n">
-        <v>15.67040838261003</v>
+        <v>15.5567680417015</v>
       </c>
       <c r="P12" t="n">
-        <v>314.3298791365711</v>
+        <v>314.4517683727943</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32945,28 +33181,28 @@
         <v>0.0963</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6773542598219809</v>
+        <v>-0.6963808401140177</v>
       </c>
       <c r="J13" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K13" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L13" t="n">
-        <v>0.104773279624085</v>
+        <v>0.110967658184348</v>
       </c>
       <c r="M13" t="n">
-        <v>12.32952209683222</v>
+        <v>12.32151775213497</v>
       </c>
       <c r="N13" t="n">
-        <v>230.6899784359072</v>
+        <v>230.5128176001599</v>
       </c>
       <c r="O13" t="n">
-        <v>15.18848176862675</v>
+        <v>15.18264857000121</v>
       </c>
       <c r="P13" t="n">
-        <v>310.0640689365252</v>
+        <v>310.2535061152614</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33023,28 +33259,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.083337326000047</v>
+        <v>-1.061823109071569</v>
       </c>
       <c r="J14" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K14" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1770266885871713</v>
+        <v>0.1727147785947495</v>
       </c>
       <c r="M14" t="n">
-        <v>14.37973952374682</v>
+        <v>14.39835140305438</v>
       </c>
       <c r="N14" t="n">
-        <v>323.0140323690491</v>
+        <v>322.3451741140174</v>
       </c>
       <c r="O14" t="n">
-        <v>17.97259114232138</v>
+        <v>17.95397376944774</v>
       </c>
       <c r="P14" t="n">
-        <v>314.0819204197149</v>
+        <v>313.8679512770451</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33101,28 +33337,28 @@
         <v>0.0604</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.84303496877106</v>
+        <v>-0.8112274215280193</v>
       </c>
       <c r="J15" t="n">
+        <v>268</v>
+      </c>
+      <c r="K15" t="n">
         <v>266</v>
       </c>
-      <c r="K15" t="n">
-        <v>264</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1487964174425461</v>
+        <v>0.1391959251742497</v>
       </c>
       <c r="M15" t="n">
-        <v>12.36162624467352</v>
+        <v>12.43101944726005</v>
       </c>
       <c r="N15" t="n">
-        <v>239.5165694783316</v>
+        <v>241.6316280339688</v>
       </c>
       <c r="O15" t="n">
-        <v>15.47632286682892</v>
+        <v>15.5445047535767</v>
       </c>
       <c r="P15" t="n">
-        <v>316.9684990251615</v>
+        <v>316.6500946193013</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33179,28 +33415,28 @@
         <v>0.0507</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7489859534295225</v>
+        <v>-0.7060855054622684</v>
       </c>
       <c r="J16" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K16" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1065204846378796</v>
+        <v>0.09488074060907892</v>
       </c>
       <c r="M16" t="n">
-        <v>13.02190613272269</v>
+        <v>13.15202734336565</v>
       </c>
       <c r="N16" t="n">
-        <v>275.1906979083379</v>
+        <v>280.3336210876244</v>
       </c>
       <c r="O16" t="n">
-        <v>16.5888727136095</v>
+        <v>16.7431663996875</v>
       </c>
       <c r="P16" t="n">
-        <v>320.896524802487</v>
+        <v>320.4652027919358</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33257,28 +33493,28 @@
         <v>0.0455</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3716163839428544</v>
+        <v>0.398647780123439</v>
       </c>
       <c r="J17" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K17" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02116917985648969</v>
+        <v>0.02445419691855166</v>
       </c>
       <c r="M17" t="n">
-        <v>14.20365674660734</v>
+        <v>14.2180099014817</v>
       </c>
       <c r="N17" t="n">
-        <v>373.6820249269133</v>
+        <v>373.9008697516917</v>
       </c>
       <c r="O17" t="n">
-        <v>19.33085680788395</v>
+        <v>19.33651648440566</v>
       </c>
       <c r="P17" t="n">
-        <v>313.5286105532646</v>
+        <v>313.2565982811148</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33335,28 +33571,28 @@
         <v>0.0552</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2023269837413736</v>
+        <v>0.2199118670104377</v>
       </c>
       <c r="J18" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K18" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02128013139122298</v>
+        <v>0.02514364920846157</v>
       </c>
       <c r="M18" t="n">
-        <v>8.408044789135506</v>
+        <v>8.443812837879721</v>
       </c>
       <c r="N18" t="n">
-        <v>110.3412933411378</v>
+        <v>110.7463659181288</v>
       </c>
       <c r="O18" t="n">
-        <v>10.50434640237734</v>
+        <v>10.52360992806788</v>
       </c>
       <c r="P18" t="n">
-        <v>330.0402191907343</v>
+        <v>329.8634515626547</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33413,28 +33649,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.009413202001159105</v>
+        <v>-0.005876214458889174</v>
       </c>
       <c r="J19" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K19" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L19" t="n">
-        <v>4.731950781777794e-05</v>
+        <v>1.871602488567881e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>8.397386621667302</v>
+        <v>8.351493160339192</v>
       </c>
       <c r="N19" t="n">
-        <v>109.5087759234966</v>
+        <v>108.7442711202078</v>
       </c>
       <c r="O19" t="n">
-        <v>10.46464408967149</v>
+        <v>10.42805212492764</v>
       </c>
       <c r="P19" t="n">
-        <v>328.6917372408401</v>
+        <v>328.6561582626344</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33491,28 +33727,28 @@
         <v>0.0559</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.146969952034243</v>
+        <v>-0.1802945745822868</v>
       </c>
       <c r="J20" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K20" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00845278883006062</v>
+        <v>0.01250328952829705</v>
       </c>
       <c r="M20" t="n">
-        <v>9.447697321323053</v>
+        <v>9.55644860160859</v>
       </c>
       <c r="N20" t="n">
-        <v>148.185401174436</v>
+        <v>151.3246019000666</v>
       </c>
       <c r="O20" t="n">
-        <v>12.17314261702523</v>
+        <v>12.30140650088707</v>
       </c>
       <c r="P20" t="n">
-        <v>328.4243058354283</v>
+        <v>328.7593970979681</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33569,28 +33805,28 @@
         <v>0.0507</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3262205607854835</v>
+        <v>-0.3642710461605805</v>
       </c>
       <c r="J21" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K21" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03528702209430046</v>
+        <v>0.04290759826264667</v>
       </c>
       <c r="M21" t="n">
-        <v>9.425929915964042</v>
+        <v>9.575431634821706</v>
       </c>
       <c r="N21" t="n">
-        <v>170.1534303002869</v>
+        <v>174.46239204631</v>
       </c>
       <c r="O21" t="n">
-        <v>13.04428726685697</v>
+        <v>13.20842125487789</v>
       </c>
       <c r="P21" t="n">
-        <v>325.2423844280045</v>
+        <v>325.6250459986278</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33647,28 +33883,28 @@
         <v>0.0745</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.43694638046488</v>
+        <v>-0.4382713021974388</v>
       </c>
       <c r="J22" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K22" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05281765735614707</v>
+        <v>0.05429832463677187</v>
       </c>
       <c r="M22" t="n">
-        <v>10.22634306119449</v>
+        <v>10.14279543825952</v>
       </c>
       <c r="N22" t="n">
-        <v>200.237626234134</v>
+        <v>197.1908009934867</v>
       </c>
       <c r="O22" t="n">
-        <v>14.15053448581127</v>
+        <v>14.04246420659446</v>
       </c>
       <c r="P22" t="n">
-        <v>318.2283263980036</v>
+        <v>318.2407956247928</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33725,28 +33961,28 @@
         <v>0.1041</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2977017472846137</v>
+        <v>-0.2799362473312106</v>
       </c>
       <c r="J23" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K23" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L23" t="n">
-        <v>0.03018499822130893</v>
+        <v>0.02722642963425792</v>
       </c>
       <c r="M23" t="n">
-        <v>9.905454157892537</v>
+        <v>9.915854135413641</v>
       </c>
       <c r="N23" t="n">
-        <v>166.531137257627</v>
+        <v>165.033532613155</v>
       </c>
       <c r="O23" t="n">
-        <v>12.90469438838545</v>
+        <v>12.84653776755259</v>
       </c>
       <c r="P23" t="n">
-        <v>309.8152930405913</v>
+        <v>309.6357362333803</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33803,28 +34039,28 @@
         <v>0.1464</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3696150855472423</v>
+        <v>-0.3487523026778729</v>
       </c>
       <c r="J24" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K24" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06957371403827062</v>
+        <v>0.06286433618949461</v>
       </c>
       <c r="M24" t="n">
-        <v>8.172541715868544</v>
+        <v>8.202557830564661</v>
       </c>
       <c r="N24" t="n">
-        <v>105.7708167602637</v>
+        <v>105.7968928112158</v>
       </c>
       <c r="O24" t="n">
-        <v>10.28449399631619</v>
+        <v>10.28576165440439</v>
       </c>
       <c r="P24" t="n">
-        <v>312.5148793341415</v>
+        <v>312.3027360781427</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33881,28 +34117,28 @@
         <v>0.0917</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.130765430149036</v>
+        <v>-0.1222226546981327</v>
       </c>
       <c r="J25" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K25" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01956926190862884</v>
+        <v>0.01729958897819373</v>
       </c>
       <c r="M25" t="n">
-        <v>5.527061170604297</v>
+        <v>5.523474324691213</v>
       </c>
       <c r="N25" t="n">
-        <v>49.59730335705861</v>
+        <v>49.51415722523329</v>
       </c>
       <c r="O25" t="n">
-        <v>7.042535293277458</v>
+        <v>7.036629677994522</v>
       </c>
       <c r="P25" t="n">
-        <v>310.1282131596541</v>
+        <v>310.0416268298319</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -33959,28 +34195,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1198281690818182</v>
+        <v>-0.1068718489062226</v>
       </c>
       <c r="J26" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K26" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01409115262021832</v>
+        <v>0.01128842677002806</v>
       </c>
       <c r="M26" t="n">
-        <v>5.913006610013187</v>
+        <v>5.924945654921578</v>
       </c>
       <c r="N26" t="n">
-        <v>58.16179349804162</v>
+        <v>58.37184990657838</v>
       </c>
       <c r="O26" t="n">
-        <v>7.626387971906597</v>
+        <v>7.640147243776024</v>
       </c>
       <c r="P26" t="n">
-        <v>314.0178296045077</v>
+        <v>313.8864987540569</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34037,28 +34273,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1256133853739089</v>
+        <v>0.1345323963049161</v>
       </c>
       <c r="J27" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K27" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L27" t="n">
-        <v>0.008839269982880982</v>
+        <v>0.01024430331409742</v>
       </c>
       <c r="M27" t="n">
-        <v>8.082293584240052</v>
+        <v>8.059472738601904</v>
       </c>
       <c r="N27" t="n">
-        <v>102.4304843608501</v>
+        <v>102.0328343520302</v>
       </c>
       <c r="O27" t="n">
-        <v>10.12079465066109</v>
+        <v>10.10113035021478</v>
       </c>
       <c r="P27" t="n">
-        <v>317.9776810869812</v>
+        <v>317.8873063916175</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34115,28 +34351,28 @@
         <v>0.0588</v>
       </c>
       <c r="I28" t="n">
-        <v>0.03302181407234449</v>
+        <v>0.0430433127262268</v>
       </c>
       <c r="J28" t="n">
+        <v>268</v>
+      </c>
+      <c r="K28" t="n">
         <v>266</v>
       </c>
-      <c r="K28" t="n">
-        <v>264</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.0004715125696252986</v>
+        <v>0.0008178069274598077</v>
       </c>
       <c r="M28" t="n">
-        <v>9.384487238805088</v>
+        <v>9.3521371211332</v>
       </c>
       <c r="N28" t="n">
-        <v>132.2385101280633</v>
+        <v>130.5241861366737</v>
       </c>
       <c r="O28" t="n">
-        <v>11.49950042949968</v>
+        <v>11.4247182081955</v>
       </c>
       <c r="P28" t="n">
-        <v>330.3872906453808</v>
+        <v>330.2841485467097</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34193,28 +34429,28 @@
         <v>0.0577</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0405246572580898</v>
+        <v>-0.02981952587540741</v>
       </c>
       <c r="J29" t="n">
+        <v>268</v>
+      </c>
+      <c r="K29" t="n">
         <v>266</v>
       </c>
-      <c r="K29" t="n">
-        <v>264</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.000756354379887747</v>
+        <v>0.000417973067278643</v>
       </c>
       <c r="M29" t="n">
-        <v>8.991326144634076</v>
+        <v>8.969052506364278</v>
       </c>
       <c r="N29" t="n">
-        <v>124.1191978515397</v>
+        <v>122.6188743282973</v>
       </c>
       <c r="O29" t="n">
-        <v>11.14087958159228</v>
+        <v>11.07334070316168</v>
       </c>
       <c r="P29" t="n">
-        <v>339.7173910279432</v>
+        <v>339.6072881360271</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34271,28 +34507,28 @@
         <v>0.0459</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2462689060845639</v>
+        <v>-0.2262509863080043</v>
       </c>
       <c r="J30" t="n">
+        <v>268</v>
+      </c>
+      <c r="K30" t="n">
         <v>266</v>
       </c>
-      <c r="K30" t="n">
-        <v>264</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.02727106535290491</v>
+        <v>0.02317804059016437</v>
       </c>
       <c r="M30" t="n">
-        <v>9.002369487448318</v>
+        <v>9.022684426209151</v>
       </c>
       <c r="N30" t="n">
-        <v>123.7550936719018</v>
+        <v>124.3957015982295</v>
       </c>
       <c r="O30" t="n">
-        <v>11.12452667181403</v>
+        <v>11.15328209982288</v>
       </c>
       <c r="P30" t="n">
-        <v>343.1979184333497</v>
+        <v>342.9931661505339</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -34349,28 +34585,28 @@
         <v>0.0523</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3718094471118471</v>
+        <v>-0.3533664848665812</v>
       </c>
       <c r="J31" t="n">
+        <v>268</v>
+      </c>
+      <c r="K31" t="n">
         <v>266</v>
       </c>
-      <c r="K31" t="n">
-        <v>264</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.06775614014160947</v>
+        <v>0.06180668843502846</v>
       </c>
       <c r="M31" t="n">
-        <v>8.824945573494949</v>
+        <v>8.859134560614853</v>
       </c>
       <c r="N31" t="n">
-        <v>108.8117775376257</v>
+        <v>109.2932364648602</v>
       </c>
       <c r="O31" t="n">
-        <v>10.4312883929851</v>
+        <v>10.45434055619292</v>
       </c>
       <c r="P31" t="n">
-        <v>342.7414417926039</v>
+        <v>342.5527861922382</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -34427,28 +34663,28 @@
         <v>0.0591</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4143598208680592</v>
+        <v>-0.3966170403770871</v>
       </c>
       <c r="J32" t="n">
+        <v>268</v>
+      </c>
+      <c r="K32" t="n">
         <v>266</v>
       </c>
-      <c r="K32" t="n">
-        <v>264</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.07283335749051556</v>
+        <v>0.06748435817166587</v>
       </c>
       <c r="M32" t="n">
-        <v>8.510514318876227</v>
+        <v>8.538270828807622</v>
       </c>
       <c r="N32" t="n">
-        <v>125.0365353258639</v>
+        <v>125.3376243844087</v>
       </c>
       <c r="O32" t="n">
-        <v>11.1819736775698</v>
+        <v>11.19542872713719</v>
       </c>
       <c r="P32" t="n">
-        <v>348.0313918495976</v>
+        <v>347.8499129946126</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -34505,28 +34741,28 @@
         <v>0.0373</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2992861593882646</v>
+        <v>-0.2491949295202613</v>
       </c>
       <c r="J33" t="n">
+        <v>268</v>
+      </c>
+      <c r="K33" t="n">
         <v>266</v>
       </c>
-      <c r="K33" t="n">
-        <v>264</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.02392474665919675</v>
+        <v>0.01624918785339724</v>
       </c>
       <c r="M33" t="n">
-        <v>11.12891585723819</v>
+        <v>11.32082660527284</v>
       </c>
       <c r="N33" t="n">
-        <v>209.056372855335</v>
+        <v>216.7791771856847</v>
       </c>
       <c r="O33" t="n">
-        <v>14.45878185931771</v>
+        <v>14.72342274016761</v>
       </c>
       <c r="P33" t="n">
-        <v>355.790992178758</v>
+        <v>355.2785137229457</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -34564,7 +34800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH267"/>
+  <dimension ref="A1:AH269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80045,7 +80281,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>-46.664448515534346,169.05524743913725</t>
+          <t>-46.66451451176842,169.0551335642755</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -80070,22 +80306,22 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>-46.66272644837337,169.05136211863007</t>
+          <t>-46.66239375510365,169.05171126751327</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>-46.66232925120647,169.05067251482677</t>
+          <t>-46.662120717831606,169.05089136421316</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>-46.66198684487428,169.04992540744348</t>
+          <t>-46.661805563108665,169.05011565852607</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>-46.66161472877874,169.0491870571332</t>
+          <t>-46.66148495587081,169.04929770195602</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -80135,17 +80371,17 @@
       </c>
       <c r="V267" t="inlineStr">
         <is>
-          <t>-46.6606784000675,169.04042206772965</t>
+          <t>-46.660569790073566,169.04041644773295</t>
         </is>
       </c>
       <c r="W267" t="inlineStr">
         <is>
-          <t>-46.66078938499911,169.03952946081282</t>
+          <t>-46.660672420418635,169.03952340983565</t>
         </is>
       </c>
       <c r="X267" t="inlineStr">
         <is>
-          <t>-46.66080520065501,169.03863212008855</t>
+          <t>-46.66072370667773,169.03862346916213</t>
         </is>
       </c>
       <c r="Y267" t="inlineStr">
@@ -80165,12 +80401,12 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>-46.661431370123644,169.0351321052745</t>
+          <t>-46.66135324674622,169.0351167585815</t>
         </is>
       </c>
       <c r="AC267" t="inlineStr">
         <is>
-          <t>-46.6616087923369,169.03428548321597</t>
+          <t>-46.66153179696186,169.03426413915102</t>
         </is>
       </c>
       <c r="AD267" t="inlineStr">
@@ -80196,6 +80432,350 @@
       <c r="AH267" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:21:03+00:00</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>-46.66544698804421,169.0563076383061</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>-46.664972125922496,169.05573548509756</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>-46.66451480122531,169.05513306482374</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>-46.664143788067285,169.05438170849598</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-46.66367033835089,169.05378345839156</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-46.663144481256914,169.0531976372215</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-46.66250597907052,169.05269993095476</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>-46.662313168246285,169.05179583949575</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>-46.66199502924627,169.05102326946312</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>-46.661708947357965,169.0502170538721</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>-46.661416968460806,169.04935566799315</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>-46.66096290250782,169.04859193118514</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>-46.66095442934639,169.04760468267972</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>-46.66094519694389,169.04664866560714</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>-46.66088828882067,169.04571919711475</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>-46.660785155202646,169.0448213746046</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>-46.66065950693372,169.04398663178924</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>-46.66052286827107,169.0431090660064</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>-46.660293110677024,169.042198822323</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>-46.66026377414895,169.0412989578631</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>-46.66051723685028,169.04041372838273</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>-46.66065211781082,169.03952235951346</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>-46.66069752819425,169.03862069021054</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>-46.66068601153082,169.03770703114137</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>-46.660855471650166,169.03683076783264</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>-46.66104155767767,169.03596142728657</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>-46.66128456587382,169.03510326682158</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>-46.66147466851084,169.0342483024771</t>
+        </is>
+      </c>
+      <c r="AD268" t="inlineStr">
+        <is>
+          <t>-46.661624668133264,169.03339807884677</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>-46.661765014120654,169.03252731706135</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
+          <t>-46.661996753751694,169.03169050633045</t>
+        </is>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>-46.662456774995896,169.03095023807714</t>
+        </is>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:21:16+00:00</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>-46.66546632398672,169.05627427458484</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>-46.66503459104797,169.0556277027831</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>-46.66455393577602,169.05506553889762</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>-46.66418043297792,169.05431847795506</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>-46.663680170432336,169.05376767837382</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-46.66313651988824,169.05320761965527</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>-46.662519313154505,169.0526859377028</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>-46.6622923293186,169.05181770888183</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>-46.66198963738423,169.0510289279933</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>-46.661717035105745,169.05020856604048</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>-46.661453714226035,169.0493243385914</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>-46.6610537067543,169.04853607670543</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>-46.66101586833868,169.04757046503886</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>-46.66091112025323,169.04666764462962</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>-46.660809644135476,169.04576299930696</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>-46.66069350867084,169.04486669819818</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>-46.66061589839708,169.04399465562955</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>-46.66053760115078,169.04310982885883</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>-46.660304519672955,169.04219941293627</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>-46.6602167008221,169.0412965215416</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>-46.66045507132768,169.04041051164964</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>-46.66057773480488,169.03951851143273</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>-46.66063790938733,169.03861436144072</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>-46.660662279318075,169.0377027907009</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>-46.66083186540784,169.0368261301032</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>-46.66098730783216,169.03595076983723</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>-46.661218379247345,169.03509026506194</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>-46.661374715792064,169.03422059448832</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>-46.66156599322823,169.03337512179863</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>-46.66172557191912,169.03251063579089</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>-46.66194238038577,169.03166751077262</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>-46.66245004304629,169.03094739104512</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0560/nzd0560.xlsx
+++ b/data/nzd0560/nzd0560.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH269"/>
+  <dimension ref="A1:AH270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29390,7 +29390,7 @@
         <v>343.75</v>
       </c>
       <c r="AF269" t="n">
-        <v>346.56</v>
+        <v>353.35</v>
       </c>
       <c r="AG269" t="n">
         <v>383.07</v>
@@ -29398,6 +29398,114 @@
       <c r="AH269" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>302.21</v>
+      </c>
+      <c r="C270" t="n">
+        <v>309.71</v>
+      </c>
+      <c r="D270" t="n">
+        <v>299.56</v>
+      </c>
+      <c r="E270" t="n">
+        <v>307.7</v>
+      </c>
+      <c r="F270" t="n">
+        <v>307.39</v>
+      </c>
+      <c r="G270" t="n">
+        <v>291.8</v>
+      </c>
+      <c r="H270" t="n">
+        <v>273.14</v>
+      </c>
+      <c r="I270" t="n">
+        <v>253.66</v>
+      </c>
+      <c r="J270" t="n">
+        <v>261.97</v>
+      </c>
+      <c r="K270" t="n">
+        <v>277.19</v>
+      </c>
+      <c r="L270" t="n">
+        <v>301.35</v>
+      </c>
+      <c r="M270" t="n">
+        <v>298.02</v>
+      </c>
+      <c r="N270" t="n">
+        <v>313.31</v>
+      </c>
+      <c r="O270" t="n">
+        <v>314.93</v>
+      </c>
+      <c r="P270" t="n">
+        <v>318.68</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>323.7</v>
+      </c>
+      <c r="R270" t="n">
+        <v>337.28</v>
+      </c>
+      <c r="S270" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="T270" t="n">
+        <v>301.89</v>
+      </c>
+      <c r="U270" t="n">
+        <v>289.7</v>
+      </c>
+      <c r="V270" t="n">
+        <v>302.96</v>
+      </c>
+      <c r="W270" t="n">
+        <v>306.58</v>
+      </c>
+      <c r="X270" t="n">
+        <v>312.26</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>308.9</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>318.6</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>320.24</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>331.06</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>329.69</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>346.8</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>344.77</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>353.39</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>367.4</v>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -29412,7 +29520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B274"/>
+  <dimension ref="A1:B275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32155,6 +32263,16 @@
       </c>
       <c r="B274" t="n">
         <v>-0.62</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>-1.11</v>
       </c>
     </row>
   </sheetData>
@@ -32323,28 +32441,28 @@
         <v>0.1765</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6989565406330271</v>
+        <v>-0.6942961581226776</v>
       </c>
       <c r="J2" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K2" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2290425003020622</v>
+        <v>0.2277624668749025</v>
       </c>
       <c r="M2" t="n">
-        <v>7.666159691017019</v>
+        <v>7.660059240414221</v>
       </c>
       <c r="N2" t="n">
-        <v>96.0497137960302</v>
+        <v>95.85238346264784</v>
       </c>
       <c r="O2" t="n">
-        <v>9.800495589307216</v>
+        <v>9.79042304819602</v>
       </c>
       <c r="P2" t="n">
-        <v>314.1720496788852</v>
+        <v>314.1242849326568</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32401,28 +32519,28 @@
         <v>0.0501</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.306154626083272</v>
+        <v>-1.298436585047714</v>
       </c>
       <c r="J3" t="n">
+        <v>269</v>
+      </c>
+      <c r="K3" t="n">
         <v>268</v>
       </c>
-      <c r="K3" t="n">
-        <v>267</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.339604838688592</v>
+        <v>0.3381722273053751</v>
       </c>
       <c r="M3" t="n">
-        <v>10.86216754303981</v>
+        <v>10.86839993436445</v>
       </c>
       <c r="N3" t="n">
-        <v>195.9471879959247</v>
+        <v>195.6686536937938</v>
       </c>
       <c r="O3" t="n">
-        <v>13.99811372992536</v>
+        <v>13.9881611977341</v>
       </c>
       <c r="P3" t="n">
-        <v>333.3667843774608</v>
+        <v>333.2883600782089</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32479,28 +32597,28 @@
         <v>0.0344</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.055134651188524</v>
+        <v>-1.051972513451592</v>
       </c>
       <c r="J4" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K4" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L4" t="n">
-        <v>0.254895915910086</v>
+        <v>0.2551763872656845</v>
       </c>
       <c r="M4" t="n">
-        <v>10.80775329183422</v>
+        <v>10.78539214182945</v>
       </c>
       <c r="N4" t="n">
-        <v>189.3557245474742</v>
+        <v>188.7177908816042</v>
       </c>
       <c r="O4" t="n">
-        <v>13.76065857971464</v>
+        <v>13.73745940418403</v>
       </c>
       <c r="P4" t="n">
-        <v>323.1605938094593</v>
+        <v>323.128119373688</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32557,28 +32675,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7589559702503681</v>
+        <v>-0.746852076548986</v>
       </c>
       <c r="J5" t="n">
+        <v>269</v>
+      </c>
+      <c r="K5" t="n">
         <v>268</v>
       </c>
-      <c r="K5" t="n">
-        <v>267</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1973895871533272</v>
+        <v>0.1923121974065166</v>
       </c>
       <c r="M5" t="n">
-        <v>9.489353351497106</v>
+        <v>9.510761111817201</v>
       </c>
       <c r="N5" t="n">
-        <v>137.1109729375301</v>
+        <v>137.6986521650012</v>
       </c>
       <c r="O5" t="n">
-        <v>11.70943948007461</v>
+        <v>11.73450689909897</v>
       </c>
       <c r="P5" t="n">
-        <v>310.6221305894932</v>
+        <v>310.4983881237925</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32635,28 +32753,28 @@
         <v>0.0596</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6638589709192545</v>
+        <v>-0.6538809228269605</v>
       </c>
       <c r="J6" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K6" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1841474068175816</v>
+        <v>0.1798227623421037</v>
       </c>
       <c r="M6" t="n">
-        <v>8.80036238628464</v>
+        <v>8.811806454290233</v>
       </c>
       <c r="N6" t="n">
-        <v>115.0881480532581</v>
+        <v>115.413924256133</v>
       </c>
       <c r="O6" t="n">
-        <v>10.72791443167115</v>
+        <v>10.74308727769318</v>
       </c>
       <c r="P6" t="n">
-        <v>310.7217726121958</v>
+        <v>310.6203768976186</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32713,28 +32831,28 @@
         <v>0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5885805980158175</v>
+        <v>-0.5858077402653763</v>
       </c>
       <c r="J7" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K7" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1552492578416703</v>
+        <v>0.1549827617544606</v>
       </c>
       <c r="M7" t="n">
-        <v>7.991836430501077</v>
+        <v>7.973823658243468</v>
       </c>
       <c r="N7" t="n">
-        <v>111.7949551536987</v>
+        <v>111.4306198344424</v>
       </c>
       <c r="O7" t="n">
-        <v>10.5733133479387</v>
+        <v>10.55607028370133</v>
       </c>
       <c r="P7" t="n">
-        <v>303.5253122420101</v>
+        <v>303.497298113691</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32791,28 +32909,28 @@
         <v>0.0326</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7843065138130018</v>
+        <v>-0.7841519884971371</v>
       </c>
       <c r="J8" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K8" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1135681869263035</v>
+        <v>0.1143319237546196</v>
       </c>
       <c r="M8" t="n">
-        <v>13.32435867551187</v>
+        <v>13.27447372296199</v>
       </c>
       <c r="N8" t="n">
-        <v>282.5300392067647</v>
+        <v>281.4559570712856</v>
       </c>
       <c r="O8" t="n">
-        <v>16.80862990272452</v>
+        <v>16.77664916100011</v>
       </c>
       <c r="P8" t="n">
-        <v>293.7829500069577</v>
+        <v>293.7813772530983</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32869,28 +32987,28 @@
         <v>0.0309</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.310875920257863</v>
+        <v>-1.315479371258313</v>
       </c>
       <c r="J9" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K9" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1780500403619499</v>
+        <v>0.1802156920153314</v>
       </c>
       <c r="M9" t="n">
-        <v>16.64379030153808</v>
+        <v>16.60599157930849</v>
       </c>
       <c r="N9" t="n">
-        <v>451.698966449717</v>
+        <v>450.118243861764</v>
       </c>
       <c r="O9" t="n">
-        <v>21.25321073272735</v>
+        <v>21.21599028708686</v>
       </c>
       <c r="P9" t="n">
-        <v>294.8089224448641</v>
+        <v>294.8569584199739</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32947,28 +33065,28 @@
         <v>0.0409</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2998580208378083</v>
+        <v>-0.3152194264170672</v>
       </c>
       <c r="J10" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K10" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01298081802094009</v>
+        <v>0.01437066990527591</v>
       </c>
       <c r="M10" t="n">
-        <v>16.33436094295222</v>
+        <v>16.36542653437297</v>
       </c>
       <c r="N10" t="n">
-        <v>404.4035680374753</v>
+        <v>404.6615381679275</v>
       </c>
       <c r="O10" t="n">
-        <v>20.10978786654587</v>
+        <v>20.11620088803866</v>
       </c>
       <c r="P10" t="n">
-        <v>291.7874869669367</v>
+        <v>291.9451379137261</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33025,28 +33143,28 @@
         <v>0.0649</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.346197931730559</v>
+        <v>-1.345597128784287</v>
       </c>
       <c r="J11" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K11" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2319606822409055</v>
+        <v>0.2332375253178954</v>
       </c>
       <c r="M11" t="n">
-        <v>14.90607193911281</v>
+        <v>14.85206896462665</v>
       </c>
       <c r="N11" t="n">
-        <v>355.9134360421472</v>
+        <v>354.5679381591292</v>
       </c>
       <c r="O11" t="n">
-        <v>18.86566818435401</v>
+        <v>18.82997445986397</v>
       </c>
       <c r="P11" t="n">
-        <v>312.1400823922202</v>
+        <v>312.1340345357662</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33103,28 +33221,28 @@
         <v>0.1385</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5566537313367739</v>
+        <v>-0.555471186676315</v>
       </c>
       <c r="J12" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K12" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07017246814613132</v>
+        <v>0.07040060626565781</v>
       </c>
       <c r="M12" t="n">
-        <v>12.33463403080022</v>
+        <v>12.29380996251623</v>
       </c>
       <c r="N12" t="n">
-        <v>242.0130319033051</v>
+        <v>241.1239402423814</v>
       </c>
       <c r="O12" t="n">
-        <v>15.5567680417015</v>
+        <v>15.52816602958577</v>
       </c>
       <c r="P12" t="n">
-        <v>314.4517683727943</v>
+        <v>314.4397514973736</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33181,28 +33299,28 @@
         <v>0.0963</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6963808401140177</v>
+        <v>-0.6919054360597215</v>
       </c>
       <c r="J13" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K13" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L13" t="n">
-        <v>0.110967658184348</v>
+        <v>0.110427383530629</v>
       </c>
       <c r="M13" t="n">
-        <v>12.32151775213497</v>
+        <v>12.30204666953428</v>
       </c>
       <c r="N13" t="n">
-        <v>230.5128176001599</v>
+        <v>229.7873278547677</v>
       </c>
       <c r="O13" t="n">
-        <v>15.18264857000121</v>
+        <v>15.15873767352571</v>
       </c>
       <c r="P13" t="n">
-        <v>310.2535061152614</v>
+        <v>310.2084589068382</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33259,28 +33377,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.061823109071569</v>
+        <v>-1.041968241486047</v>
       </c>
       <c r="J14" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K14" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1727147785947495</v>
+        <v>0.1672556752886672</v>
       </c>
       <c r="M14" t="n">
-        <v>14.39835140305438</v>
+        <v>14.46522617961917</v>
       </c>
       <c r="N14" t="n">
-        <v>322.3451741140174</v>
+        <v>324.01694393369</v>
       </c>
       <c r="O14" t="n">
-        <v>17.95397376944774</v>
+        <v>18.0004706586714</v>
       </c>
       <c r="P14" t="n">
-        <v>313.8679512770451</v>
+        <v>313.6684354680425</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33337,28 +33455,28 @@
         <v>0.0604</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8112274215280193</v>
+        <v>-0.7973813572596451</v>
       </c>
       <c r="J15" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K15" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1391959251742497</v>
+        <v>0.135327449598896</v>
       </c>
       <c r="M15" t="n">
-        <v>12.43101944726005</v>
+        <v>12.45827402865493</v>
       </c>
       <c r="N15" t="n">
-        <v>241.6316280339688</v>
+        <v>242.185490764004</v>
       </c>
       <c r="O15" t="n">
-        <v>15.5445047535767</v>
+        <v>15.56230994306449</v>
       </c>
       <c r="P15" t="n">
-        <v>316.6500946193013</v>
+        <v>316.5099986832329</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33415,28 +33533,28 @@
         <v>0.0507</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7060855054622684</v>
+        <v>-0.6942474930731205</v>
       </c>
       <c r="J16" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K16" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09488074060907892</v>
+        <v>0.09235076123628216</v>
       </c>
       <c r="M16" t="n">
-        <v>13.15202734336565</v>
+        <v>13.164727380261</v>
       </c>
       <c r="N16" t="n">
-        <v>280.3336210876244</v>
+        <v>280.3522431663983</v>
       </c>
       <c r="O16" t="n">
-        <v>16.7431663996875</v>
+        <v>16.74372250028047</v>
       </c>
       <c r="P16" t="n">
-        <v>320.4652027919358</v>
+        <v>320.3449063457502</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33493,28 +33611,28 @@
         <v>0.0455</v>
       </c>
       <c r="I17" t="n">
-        <v>0.398647780123439</v>
+        <v>0.3985420335947724</v>
       </c>
       <c r="J17" t="n">
+        <v>269</v>
+      </c>
+      <c r="K17" t="n">
         <v>268</v>
       </c>
-      <c r="K17" t="n">
-        <v>267</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.02445419691855166</v>
+        <v>0.02462763595051287</v>
       </c>
       <c r="M17" t="n">
-        <v>14.2180099014817</v>
+        <v>14.16560686067633</v>
       </c>
       <c r="N17" t="n">
-        <v>373.9008697516917</v>
+        <v>372.5058020775578</v>
       </c>
       <c r="O17" t="n">
-        <v>19.33651648440566</v>
+        <v>19.30040937590594</v>
       </c>
       <c r="P17" t="n">
-        <v>313.2565982811148</v>
+        <v>313.2576740015668</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33571,28 +33689,28 @@
         <v>0.0552</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2199118670104377</v>
+        <v>0.2210068719585484</v>
       </c>
       <c r="J18" t="n">
+        <v>269</v>
+      </c>
+      <c r="K18" t="n">
         <v>268</v>
       </c>
-      <c r="K18" t="n">
-        <v>267</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.02514364920846157</v>
+        <v>0.02557931779028499</v>
       </c>
       <c r="M18" t="n">
-        <v>8.443812837879721</v>
+        <v>8.418446167759772</v>
       </c>
       <c r="N18" t="n">
-        <v>110.7463659181288</v>
+        <v>110.3422437466785</v>
       </c>
       <c r="O18" t="n">
-        <v>10.52360992806788</v>
+        <v>10.50439164096039</v>
       </c>
       <c r="P18" t="n">
-        <v>329.8634515626547</v>
+        <v>329.8523250351672</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33649,28 +33767,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.005876214458889174</v>
+        <v>-0.005181114179731796</v>
       </c>
       <c r="J19" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K19" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L19" t="n">
-        <v>1.871602488567881e-05</v>
+        <v>1.466338454847449e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>8.351493160339192</v>
+        <v>8.323661296364646</v>
       </c>
       <c r="N19" t="n">
-        <v>108.7442711202078</v>
+        <v>108.3436745538384</v>
       </c>
       <c r="O19" t="n">
-        <v>10.42805212492764</v>
+        <v>10.40882676164026</v>
       </c>
       <c r="P19" t="n">
-        <v>328.6561582626344</v>
+        <v>328.6490947378993</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33727,28 +33845,28 @@
         <v>0.0559</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1802945745822868</v>
+        <v>-0.1956762305214599</v>
       </c>
       <c r="J20" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K20" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01250328952829705</v>
+        <v>0.01463692076394529</v>
       </c>
       <c r="M20" t="n">
-        <v>9.55644860160859</v>
+        <v>9.605399845938583</v>
       </c>
       <c r="N20" t="n">
-        <v>151.3246019000666</v>
+        <v>152.5529245456801</v>
       </c>
       <c r="O20" t="n">
-        <v>12.30140650088707</v>
+        <v>12.3512317015624</v>
       </c>
       <c r="P20" t="n">
-        <v>328.7593970979681</v>
+        <v>328.9157036201363</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33805,28 +33923,28 @@
         <v>0.0507</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3642710461605805</v>
+        <v>-0.3825562138856717</v>
       </c>
       <c r="J21" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K21" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04290759826264667</v>
+        <v>0.04681688146936314</v>
       </c>
       <c r="M21" t="n">
-        <v>9.575431634821706</v>
+        <v>9.645296022867541</v>
       </c>
       <c r="N21" t="n">
-        <v>174.46239204631</v>
+        <v>176.3446176603691</v>
       </c>
       <c r="O21" t="n">
-        <v>13.20842125487789</v>
+        <v>13.27948107647167</v>
       </c>
       <c r="P21" t="n">
-        <v>325.6250459986278</v>
+        <v>325.8108576554268</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33883,28 +34001,28 @@
         <v>0.0745</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4382713021974388</v>
+        <v>-0.4407968893280285</v>
       </c>
       <c r="J22" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K22" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05429832463677187</v>
+        <v>0.05528409582217353</v>
       </c>
       <c r="M22" t="n">
-        <v>10.14279543825952</v>
+        <v>10.11982897511122</v>
       </c>
       <c r="N22" t="n">
-        <v>197.1908009934867</v>
+        <v>196.5060313287305</v>
       </c>
       <c r="O22" t="n">
-        <v>14.04246420659446</v>
+        <v>14.01806089759673</v>
       </c>
       <c r="P22" t="n">
-        <v>318.2407956247928</v>
+        <v>318.2664603349108</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33961,28 +34079,28 @@
         <v>0.1041</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2799362473312106</v>
+        <v>-0.2768771977511841</v>
       </c>
       <c r="J23" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K23" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02722642963425792</v>
+        <v>0.02684193563748694</v>
       </c>
       <c r="M23" t="n">
-        <v>9.915854135413641</v>
+        <v>9.89338716370778</v>
       </c>
       <c r="N23" t="n">
-        <v>165.033532613155</v>
+        <v>164.490857192251</v>
       </c>
       <c r="O23" t="n">
-        <v>12.84653776755259</v>
+        <v>12.82539890967338</v>
       </c>
       <c r="P23" t="n">
-        <v>309.6357362333803</v>
+        <v>309.6046505425493</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34039,28 +34157,28 @@
         <v>0.1464</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3487523026778729</v>
+        <v>-0.3422617153077167</v>
       </c>
       <c r="J24" t="n">
+        <v>269</v>
+      </c>
+      <c r="K24" t="n">
         <v>268</v>
       </c>
-      <c r="K24" t="n">
-        <v>267</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.06286433618949461</v>
+        <v>0.0609633572620073</v>
       </c>
       <c r="M24" t="n">
-        <v>8.202557830564661</v>
+        <v>8.199943433151002</v>
       </c>
       <c r="N24" t="n">
-        <v>105.7968928112158</v>
+        <v>105.7165699894523</v>
       </c>
       <c r="O24" t="n">
-        <v>10.28576165440439</v>
+        <v>10.2818563493881</v>
       </c>
       <c r="P24" t="n">
-        <v>312.3027360781427</v>
+        <v>312.2362452723233</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34117,28 +34235,28 @@
         <v>0.0917</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1222226546981327</v>
+        <v>-0.1207423580002079</v>
       </c>
       <c r="J25" t="n">
+        <v>269</v>
+      </c>
+      <c r="K25" t="n">
         <v>268</v>
       </c>
-      <c r="K25" t="n">
-        <v>267</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.01729958897819373</v>
+        <v>0.01701489093991659</v>
       </c>
       <c r="M25" t="n">
-        <v>5.523474324691213</v>
+        <v>5.509242989697511</v>
       </c>
       <c r="N25" t="n">
-        <v>49.51415722523329</v>
+        <v>49.34575862773934</v>
       </c>
       <c r="O25" t="n">
-        <v>7.036629677994522</v>
+        <v>7.024653630446084</v>
       </c>
       <c r="P25" t="n">
-        <v>310.0416268298319</v>
+        <v>310.0264623902082</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34195,28 +34313,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1068718489062226</v>
+        <v>-0.1015642659416837</v>
       </c>
       <c r="J26" t="n">
+        <v>269</v>
+      </c>
+      <c r="K26" t="n">
         <v>268</v>
       </c>
-      <c r="K26" t="n">
-        <v>267</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.01128842677002806</v>
+        <v>0.01024880687735052</v>
       </c>
       <c r="M26" t="n">
-        <v>5.924945654921578</v>
+        <v>5.925287558657029</v>
       </c>
       <c r="N26" t="n">
-        <v>58.37184990657838</v>
+        <v>58.36430888420927</v>
       </c>
       <c r="O26" t="n">
-        <v>7.640147243776024</v>
+        <v>7.639653714940833</v>
       </c>
       <c r="P26" t="n">
-        <v>313.8864987540569</v>
+        <v>313.8321268693354</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34273,28 +34391,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1345323963049161</v>
+        <v>0.1336698351586463</v>
       </c>
       <c r="J27" t="n">
+        <v>269</v>
+      </c>
+      <c r="K27" t="n">
         <v>268</v>
       </c>
-      <c r="K27" t="n">
-        <v>267</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.01024430331409742</v>
+        <v>0.01019271967674318</v>
       </c>
       <c r="M27" t="n">
-        <v>8.059472738601904</v>
+        <v>8.034904130528112</v>
       </c>
       <c r="N27" t="n">
-        <v>102.0328343520302</v>
+        <v>101.6576681309373</v>
       </c>
       <c r="O27" t="n">
-        <v>10.10113035021478</v>
+        <v>10.08254274133947</v>
       </c>
       <c r="P27" t="n">
-        <v>317.8873063916175</v>
+        <v>317.8961426313002</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34351,28 +34469,28 @@
         <v>0.0588</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0430433127262268</v>
+        <v>0.04277791617377335</v>
       </c>
       <c r="J28" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K28" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0008178069274598077</v>
+        <v>0.0008141254726954372</v>
       </c>
       <c r="M28" t="n">
-        <v>9.3521371211332</v>
+        <v>9.318879737515539</v>
       </c>
       <c r="N28" t="n">
-        <v>130.5241861366737</v>
+        <v>130.0358484277286</v>
       </c>
       <c r="O28" t="n">
-        <v>11.4247182081955</v>
+        <v>11.40332620018074</v>
       </c>
       <c r="P28" t="n">
-        <v>330.2841485467097</v>
+        <v>330.2868919792601</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34429,28 +34547,28 @@
         <v>0.0577</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.02981952587540741</v>
+        <v>-0.03630241726163379</v>
       </c>
       <c r="J29" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K29" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L29" t="n">
-        <v>0.000417973067278643</v>
+        <v>0.0006226537761863105</v>
       </c>
       <c r="M29" t="n">
-        <v>8.969052506364278</v>
+        <v>8.976038828198657</v>
       </c>
       <c r="N29" t="n">
-        <v>122.6188743282973</v>
+        <v>122.468067773995</v>
       </c>
       <c r="O29" t="n">
-        <v>11.07334070316168</v>
+        <v>11.06652916564155</v>
       </c>
       <c r="P29" t="n">
-        <v>339.6072881360271</v>
+        <v>339.6743024777201</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34507,28 +34625,28 @@
         <v>0.0459</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2262509863080043</v>
+        <v>-0.2192779361910435</v>
       </c>
       <c r="J30" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K30" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02317804059016437</v>
+        <v>0.02190855676281334</v>
       </c>
       <c r="M30" t="n">
-        <v>9.022684426209151</v>
+        <v>9.018847068112782</v>
       </c>
       <c r="N30" t="n">
-        <v>124.3957015982295</v>
+        <v>124.2866445965227</v>
       </c>
       <c r="O30" t="n">
-        <v>11.15328209982288</v>
+        <v>11.14839201842682</v>
       </c>
       <c r="P30" t="n">
-        <v>342.9931661505339</v>
+        <v>342.921084985612</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -34585,28 +34703,28 @@
         <v>0.0523</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3533664848665812</v>
+        <v>-0.3451182788520397</v>
       </c>
       <c r="J31" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K31" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L31" t="n">
-        <v>0.06180668843502846</v>
+        <v>0.05930651262437181</v>
       </c>
       <c r="M31" t="n">
-        <v>8.859134560614853</v>
+        <v>8.870183741680055</v>
       </c>
       <c r="N31" t="n">
-        <v>109.2932364648602</v>
+        <v>109.3831880047623</v>
       </c>
       <c r="O31" t="n">
-        <v>10.45434055619292</v>
+        <v>10.45864178585165</v>
       </c>
       <c r="P31" t="n">
-        <v>342.5527861922382</v>
+        <v>342.4675236044077</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -34663,28 +34781,28 @@
         <v>0.0591</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3966170403770871</v>
+        <v>-0.3804560588625311</v>
       </c>
       <c r="J32" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K32" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L32" t="n">
-        <v>0.06748435817166587</v>
+        <v>0.06215487869781444</v>
       </c>
       <c r="M32" t="n">
-        <v>8.538270828807622</v>
+        <v>8.592027656826227</v>
       </c>
       <c r="N32" t="n">
-        <v>125.3376243844087</v>
+        <v>126.4543614065245</v>
       </c>
       <c r="O32" t="n">
-        <v>11.19542872713719</v>
+        <v>11.24519281322132</v>
       </c>
       <c r="P32" t="n">
-        <v>347.8499129946126</v>
+        <v>347.6833119453312</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -34741,28 +34859,28 @@
         <v>0.0373</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2491949295202613</v>
+        <v>-0.2358760562528003</v>
       </c>
       <c r="J33" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K33" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L33" t="n">
-        <v>0.01624918785339724</v>
+        <v>0.01460988408188169</v>
       </c>
       <c r="M33" t="n">
-        <v>11.32082660527284</v>
+        <v>11.35141614958413</v>
       </c>
       <c r="N33" t="n">
-        <v>216.7791771856847</v>
+        <v>217.2691425257557</v>
       </c>
       <c r="O33" t="n">
-        <v>14.72342274016761</v>
+        <v>14.74005232439002</v>
       </c>
       <c r="P33" t="n">
-        <v>355.2785137229457</v>
+        <v>355.1408351053448</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -34800,7 +34918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH269"/>
+  <dimension ref="A1:AH270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80765,7 +80883,7 @@
       </c>
       <c r="AF269" t="inlineStr">
         <is>
-          <t>-46.66194238038577,169.03166751077262</t>
+          <t>-46.66200098279112,169.03169229487563</t>
         </is>
       </c>
       <c r="AG269" t="inlineStr">
@@ -80776,6 +80894,178 @@
       <c r="AH269" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>-46.66549318587744,169.05622792494475</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>-46.665079109684775,169.05555088650655</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>-46.664562851037445,169.0550501557589</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>-46.66415247169883,169.05436672496316</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>-46.66368632302199,169.05375780375857</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-46.66313475069507,169.05320983797347</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>-46.66263465654288,169.05256489195784</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>-46.66214929836813,169.05196781193402</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>-46.66186642596357,169.05115823274198</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>-46.6616338988535,169.05029581470933</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>-46.66145115597688,169.0493265197537</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>-46.66116793629567,169.04846581281603</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>-46.661091659864354,169.04752825382033</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>-46.66090465743212,169.04667124409656</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>-46.66073553178168,169.04580427702425</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>-46.66057607853951,169.0449247727604</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>-46.66054116638258,169.0440084060609</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>-46.66051675951608,169.0431087497018</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>-46.660311886111245,169.0421997942772</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>-46.66024553772655,169.0412980140208</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>-46.660407818343494,169.04040806656243</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>-46.660483498363,169.03951363627334</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>-46.660578649189425,169.03860807074832</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>-46.66063926085598,169.03769867779536</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>-46.66082981656416,169.03682572758345</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>-46.660948023460804,169.0359430523851</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>-46.66114800584785,169.03507644087833</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>-46.661240680248056,169.0341834385116</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>-46.66155957023544,169.03337260875176</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>-46.66173437521154,169.0325143589609</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>-46.662001328018825,169.03169244087934</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>-46.66231479989339,169.03089019504137</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0560/nzd0560.xlsx
+++ b/data/nzd0560/nzd0560.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH270"/>
+  <dimension ref="A1:AH272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29411,7 +29411,7 @@
         <v>302.21</v>
       </c>
       <c r="C270" t="n">
-        <v>309.71</v>
+        <v>302.7</v>
       </c>
       <c r="D270" t="n">
         <v>299.56</v>
@@ -29489,7 +29489,7 @@
         <v>331.06</v>
       </c>
       <c r="AC270" t="n">
-        <v>329.69</v>
+        <v>339.25</v>
       </c>
       <c r="AD270" t="n">
         <v>346.8</v>
@@ -29504,6 +29504,222 @@
         <v>367.4</v>
       </c>
       <c r="AH270" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>296.09</v>
+      </c>
+      <c r="C271" t="n">
+        <v>298.06</v>
+      </c>
+      <c r="D271" t="n">
+        <v>290.85</v>
+      </c>
+      <c r="E271" t="n">
+        <v>302.23</v>
+      </c>
+      <c r="F271" t="n">
+        <v>304.62</v>
+      </c>
+      <c r="G271" t="n">
+        <v>291.82</v>
+      </c>
+      <c r="H271" t="n">
+        <v>273.67</v>
+      </c>
+      <c r="I271" t="n">
+        <v>254.02</v>
+      </c>
+      <c r="J271" t="n">
+        <v>276.13</v>
+      </c>
+      <c r="K271" t="n">
+        <v>290.11</v>
+      </c>
+      <c r="L271" t="n">
+        <v>310.6</v>
+      </c>
+      <c r="M271" t="n">
+        <v>306.68</v>
+      </c>
+      <c r="N271" t="n">
+        <v>318.35</v>
+      </c>
+      <c r="O271" t="n">
+        <v>317.3</v>
+      </c>
+      <c r="P271" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>323.81</v>
+      </c>
+      <c r="R271" t="n">
+        <v>339.56</v>
+      </c>
+      <c r="S271" t="n">
+        <v>332.89</v>
+      </c>
+      <c r="T271" t="n">
+        <v>311.01</v>
+      </c>
+      <c r="U271" t="n">
+        <v>301.85</v>
+      </c>
+      <c r="V271" t="n">
+        <v>312.13</v>
+      </c>
+      <c r="W271" t="n">
+        <v>312.89</v>
+      </c>
+      <c r="X271" t="n">
+        <v>314.79</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>314.55</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>318.95</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>320.02</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>332.8</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>344.24</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>348.25</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>348.46</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>364.89</v>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:30+00:00</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>301.89</v>
+      </c>
+      <c r="C272" t="n">
+        <v>305.26</v>
+      </c>
+      <c r="D272" t="n">
+        <v>290.85</v>
+      </c>
+      <c r="E272" t="n">
+        <v>305.3</v>
+      </c>
+      <c r="F272" t="n">
+        <v>308.87</v>
+      </c>
+      <c r="G272" t="n">
+        <v>300.09</v>
+      </c>
+      <c r="H272" t="n">
+        <v>273.67</v>
+      </c>
+      <c r="I272" t="n">
+        <v>254.02</v>
+      </c>
+      <c r="J272" t="n">
+        <v>276.13</v>
+      </c>
+      <c r="K272" t="n">
+        <v>299.52</v>
+      </c>
+      <c r="L272" t="n">
+        <v>311.33</v>
+      </c>
+      <c r="M272" t="n">
+        <v>311.48</v>
+      </c>
+      <c r="N272" t="n">
+        <v>316.14</v>
+      </c>
+      <c r="O272" t="n">
+        <v>318.08</v>
+      </c>
+      <c r="P272" t="n">
+        <v>320.75</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>326.09</v>
+      </c>
+      <c r="R272" t="n">
+        <v>339.27</v>
+      </c>
+      <c r="S272" t="n">
+        <v>330.61</v>
+      </c>
+      <c r="T272" t="n">
+        <v>312.88</v>
+      </c>
+      <c r="U272" t="n">
+        <v>304.19</v>
+      </c>
+      <c r="V272" t="n">
+        <v>309.24</v>
+      </c>
+      <c r="W272" t="n">
+        <v>306.82</v>
+      </c>
+      <c r="X272" t="n">
+        <v>307.98</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>311.15</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>314.89</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>321.94</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>334.07</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>345.01</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>348.8</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>348.46</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>364.89</v>
+      </c>
+      <c r="AH272" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29520,7 +29736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B275"/>
+  <dimension ref="A1:B277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32273,6 +32489,26 @@
       </c>
       <c r="B275" t="n">
         <v>-1.11</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -32441,28 +32677,28 @@
         <v>0.1765</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6942961581226776</v>
+        <v>-0.6895162796801195</v>
       </c>
       <c r="J2" t="n">
+        <v>271</v>
+      </c>
+      <c r="K2" t="n">
         <v>269</v>
       </c>
-      <c r="K2" t="n">
-        <v>267</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2277624668749025</v>
+        <v>0.2278134224582106</v>
       </c>
       <c r="M2" t="n">
-        <v>7.660059240414221</v>
+        <v>7.625753142424597</v>
       </c>
       <c r="N2" t="n">
-        <v>95.85238346264784</v>
+        <v>95.28837508945549</v>
       </c>
       <c r="O2" t="n">
-        <v>9.79042304819602</v>
+        <v>9.761576465379733</v>
       </c>
       <c r="P2" t="n">
-        <v>314.1242849326568</v>
+        <v>314.0749064544814</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32519,28 +32755,28 @@
         <v>0.0501</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.298436585047714</v>
+        <v>-1.298950538140228</v>
       </c>
       <c r="J3" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K3" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3381722273053751</v>
+        <v>0.3421014797747425</v>
       </c>
       <c r="M3" t="n">
-        <v>10.86839993436445</v>
+        <v>10.78853442610564</v>
       </c>
       <c r="N3" t="n">
-        <v>195.6686536937938</v>
+        <v>194.001007732044</v>
       </c>
       <c r="O3" t="n">
-        <v>13.9881611977341</v>
+        <v>13.92842445260927</v>
       </c>
       <c r="P3" t="n">
-        <v>333.2883600782089</v>
+        <v>333.2932054474334</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32597,28 +32833,28 @@
         <v>0.0344</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.051972513451592</v>
+        <v>-1.057804379067479</v>
       </c>
       <c r="J4" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K4" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2551763872656845</v>
+        <v>0.2601815450550254</v>
       </c>
       <c r="M4" t="n">
-        <v>10.78539214182945</v>
+        <v>10.732437522416</v>
       </c>
       <c r="N4" t="n">
-        <v>188.7177908816042</v>
+        <v>187.4354149492804</v>
       </c>
       <c r="O4" t="n">
-        <v>13.73745940418403</v>
+        <v>13.6907054219014</v>
       </c>
       <c r="P4" t="n">
-        <v>323.128119373688</v>
+        <v>323.1884050728948</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32675,28 +32911,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.746852076548986</v>
+        <v>-0.7284825195761964</v>
       </c>
       <c r="J5" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K5" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1923121974065166</v>
+        <v>0.1856431900025119</v>
       </c>
       <c r="M5" t="n">
-        <v>9.510761111817201</v>
+        <v>9.52703787639002</v>
       </c>
       <c r="N5" t="n">
-        <v>137.6986521650012</v>
+        <v>137.9637372480871</v>
       </c>
       <c r="O5" t="n">
-        <v>11.73450689909897</v>
+        <v>11.7457965778438</v>
       </c>
       <c r="P5" t="n">
-        <v>310.4983881237925</v>
+        <v>310.3093112553299</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32753,28 +32989,28 @@
         <v>0.0596</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6538809228269605</v>
+        <v>-0.6351029396111394</v>
       </c>
       <c r="J6" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K6" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1798227623421037</v>
+        <v>0.1719187097514536</v>
       </c>
       <c r="M6" t="n">
-        <v>8.811806454290233</v>
+        <v>8.831390674018934</v>
       </c>
       <c r="N6" t="n">
-        <v>115.413924256133</v>
+        <v>115.9316187185398</v>
       </c>
       <c r="O6" t="n">
-        <v>10.74308727769318</v>
+        <v>10.76715462499447</v>
       </c>
       <c r="P6" t="n">
-        <v>310.6203768976186</v>
+        <v>310.4282411447932</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32831,28 +33067,28 @@
         <v>0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5858077402653763</v>
+        <v>-0.5744442859594306</v>
       </c>
       <c r="J7" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K7" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1549827617544606</v>
+        <v>0.1512476896033659</v>
       </c>
       <c r="M7" t="n">
-        <v>7.973823658243468</v>
+        <v>7.962822144966836</v>
       </c>
       <c r="N7" t="n">
-        <v>111.4306198344424</v>
+        <v>111.2078801538178</v>
       </c>
       <c r="O7" t="n">
-        <v>10.55607028370133</v>
+        <v>10.54551469364193</v>
       </c>
       <c r="P7" t="n">
-        <v>303.497298113691</v>
+        <v>303.3816357995128</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32909,28 +33145,28 @@
         <v>0.0326</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7841519884971371</v>
+        <v>-0.7829564521176895</v>
       </c>
       <c r="J8" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K8" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1143319237546196</v>
+        <v>0.1156429152302436</v>
       </c>
       <c r="M8" t="n">
-        <v>13.27447372296199</v>
+        <v>13.18018788117096</v>
       </c>
       <c r="N8" t="n">
-        <v>281.4559570712856</v>
+        <v>279.3370613393631</v>
       </c>
       <c r="O8" t="n">
-        <v>16.77664916100011</v>
+        <v>16.71337971026097</v>
       </c>
       <c r="P8" t="n">
-        <v>293.7813772530983</v>
+        <v>293.7691276398393</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32987,28 +33223,28 @@
         <v>0.0309</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.315479371258313</v>
+        <v>-1.323687285861321</v>
       </c>
       <c r="J9" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K9" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1802156920153314</v>
+        <v>0.1843959932297996</v>
       </c>
       <c r="M9" t="n">
-        <v>16.60599157930849</v>
+        <v>16.52507962637361</v>
       </c>
       <c r="N9" t="n">
-        <v>450.118243861764</v>
+        <v>446.9341312609873</v>
       </c>
       <c r="O9" t="n">
-        <v>21.21599028708686</v>
+        <v>21.14081671225091</v>
       </c>
       <c r="P9" t="n">
-        <v>294.8569584199739</v>
+        <v>294.9431585178781</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33065,28 +33301,28 @@
         <v>0.0409</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3152194264170672</v>
+        <v>-0.3255091830887916</v>
       </c>
       <c r="J10" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K10" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01437066990527591</v>
+        <v>0.01552860484720719</v>
       </c>
       <c r="M10" t="n">
-        <v>16.36542653437297</v>
+        <v>16.30223041379558</v>
       </c>
       <c r="N10" t="n">
-        <v>404.6615381679275</v>
+        <v>401.9797278560905</v>
       </c>
       <c r="O10" t="n">
-        <v>20.11620088803866</v>
+        <v>20.04943210806956</v>
       </c>
       <c r="P10" t="n">
-        <v>291.9451379137261</v>
+        <v>292.0514674388124</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33143,28 +33379,28 @@
         <v>0.0649</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.345597128784287</v>
+        <v>-1.319284766179406</v>
       </c>
       <c r="J11" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K11" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2332375253178954</v>
+        <v>0.2277275484016821</v>
       </c>
       <c r="M11" t="n">
-        <v>14.85206896462665</v>
+        <v>14.84779595101091</v>
       </c>
       <c r="N11" t="n">
-        <v>354.5679381591292</v>
+        <v>354.6248794772275</v>
       </c>
       <c r="O11" t="n">
-        <v>18.82997445986397</v>
+        <v>18.83148638523331</v>
       </c>
       <c r="P11" t="n">
-        <v>312.1340345357662</v>
+        <v>311.8673091083413</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33221,28 +33457,28 @@
         <v>0.1385</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.555471186676315</v>
+        <v>-0.5397808658492177</v>
       </c>
       <c r="J12" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K12" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07040060626565781</v>
+        <v>0.06747519475329378</v>
       </c>
       <c r="M12" t="n">
-        <v>12.29380996251623</v>
+        <v>12.26883193732246</v>
       </c>
       <c r="N12" t="n">
-        <v>241.1239402423814</v>
+        <v>240.2785720464886</v>
       </c>
       <c r="O12" t="n">
-        <v>15.52816602958577</v>
+        <v>15.50092165151765</v>
       </c>
       <c r="P12" t="n">
-        <v>314.4397514973736</v>
+        <v>314.279239287217</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33299,28 +33535,28 @@
         <v>0.0963</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6919054360597215</v>
+        <v>-0.6674150234077891</v>
       </c>
       <c r="J13" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K13" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L13" t="n">
-        <v>0.110427383530629</v>
+        <v>0.1041270112584582</v>
       </c>
       <c r="M13" t="n">
-        <v>12.30204666953428</v>
+        <v>12.35696384639684</v>
       </c>
       <c r="N13" t="n">
-        <v>229.7873278547677</v>
+        <v>230.318912065298</v>
       </c>
       <c r="O13" t="n">
-        <v>15.15873767352571</v>
+        <v>15.17626146537078</v>
       </c>
       <c r="P13" t="n">
-        <v>310.2084589068382</v>
+        <v>309.9602644986816</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33377,28 +33613,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.041968241486047</v>
+        <v>-0.9973813803014879</v>
       </c>
       <c r="J14" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K14" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1672556752886672</v>
+        <v>0.1545768113713729</v>
       </c>
       <c r="M14" t="n">
-        <v>14.46522617961917</v>
+        <v>14.62760756923798</v>
       </c>
       <c r="N14" t="n">
-        <v>324.01694393369</v>
+        <v>328.9158986797029</v>
       </c>
       <c r="O14" t="n">
-        <v>18.0004706586714</v>
+        <v>18.13603867110188</v>
       </c>
       <c r="P14" t="n">
-        <v>313.6684354680425</v>
+        <v>313.217412941208</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33455,28 +33691,28 @@
         <v>0.0604</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7973813572596451</v>
+        <v>-0.7663162393761522</v>
       </c>
       <c r="J15" t="n">
+        <v>271</v>
+      </c>
+      <c r="K15" t="n">
         <v>269</v>
       </c>
-      <c r="K15" t="n">
-        <v>267</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.135327449598896</v>
+        <v>0.1263447830641402</v>
       </c>
       <c r="M15" t="n">
-        <v>12.45827402865493</v>
+        <v>12.52806744052877</v>
       </c>
       <c r="N15" t="n">
-        <v>242.185490764004</v>
+        <v>244.0638178372675</v>
       </c>
       <c r="O15" t="n">
-        <v>15.56230994306449</v>
+        <v>15.62254197745257</v>
       </c>
       <c r="P15" t="n">
-        <v>316.5099986832329</v>
+        <v>316.1935575743109</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33533,28 +33769,28 @@
         <v>0.0507</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6942474930731205</v>
+        <v>-0.6694354515787077</v>
       </c>
       <c r="J16" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K16" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09235076123628216</v>
+        <v>0.08700157979508061</v>
       </c>
       <c r="M16" t="n">
-        <v>13.164727380261</v>
+        <v>13.1940455242648</v>
       </c>
       <c r="N16" t="n">
-        <v>280.3522431663983</v>
+        <v>280.6235586634397</v>
       </c>
       <c r="O16" t="n">
-        <v>16.74372250028047</v>
+        <v>16.75182254751523</v>
       </c>
       <c r="P16" t="n">
-        <v>320.3449063457502</v>
+        <v>320.0910702996455</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33611,28 +33847,28 @@
         <v>0.0455</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3985420335947724</v>
+        <v>0.3999751802236621</v>
       </c>
       <c r="J17" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K17" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02462763595051287</v>
+        <v>0.02517949609776371</v>
       </c>
       <c r="M17" t="n">
-        <v>14.16560686067633</v>
+        <v>14.06793452620234</v>
       </c>
       <c r="N17" t="n">
-        <v>372.5058020775578</v>
+        <v>369.7636830286764</v>
       </c>
       <c r="O17" t="n">
-        <v>19.30040937590594</v>
+        <v>19.2292403133529</v>
       </c>
       <c r="P17" t="n">
-        <v>313.2576740015668</v>
+        <v>313.2429730446366</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33689,28 +33925,28 @@
         <v>0.0552</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2210068719585484</v>
+        <v>0.2260456617973897</v>
       </c>
       <c r="J18" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K18" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02557931779028499</v>
+        <v>0.02711272366097939</v>
       </c>
       <c r="M18" t="n">
-        <v>8.418446167759772</v>
+        <v>8.383810770887349</v>
       </c>
       <c r="N18" t="n">
-        <v>110.3422437466785</v>
+        <v>109.6216992584623</v>
       </c>
       <c r="O18" t="n">
-        <v>10.50439164096039</v>
+        <v>10.47003816891144</v>
       </c>
       <c r="P18" t="n">
-        <v>329.8523250351672</v>
+        <v>329.800785879448</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33767,28 +34003,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.005181114179731796</v>
+        <v>-0.0007172439740164237</v>
       </c>
       <c r="J19" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K19" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L19" t="n">
-        <v>1.466338454847449e-05</v>
+        <v>2.852111821161074e-07</v>
       </c>
       <c r="M19" t="n">
-        <v>8.323661296364646</v>
+        <v>8.282767853200681</v>
       </c>
       <c r="N19" t="n">
-        <v>108.3436745538384</v>
+        <v>107.6294125047633</v>
       </c>
       <c r="O19" t="n">
-        <v>10.40882676164026</v>
+        <v>10.37445962471122</v>
       </c>
       <c r="P19" t="n">
-        <v>328.6490947378993</v>
+        <v>328.6034564816103</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33845,28 +34081,28 @@
         <v>0.0559</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1956762305214599</v>
+        <v>-0.2118641429073952</v>
       </c>
       <c r="J20" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K20" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01463692076394529</v>
+        <v>0.01726832784811572</v>
       </c>
       <c r="M20" t="n">
-        <v>9.605399845938583</v>
+        <v>9.622452058988291</v>
       </c>
       <c r="N20" t="n">
-        <v>152.5529245456801</v>
+        <v>152.4275304444855</v>
       </c>
       <c r="O20" t="n">
-        <v>12.3512317015624</v>
+        <v>12.34615448001868</v>
       </c>
       <c r="P20" t="n">
-        <v>328.9157036201363</v>
+        <v>329.0812770441402</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33923,28 +34159,28 @@
         <v>0.0507</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3825562138856717</v>
+        <v>-0.3998837237603018</v>
       </c>
       <c r="J21" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K21" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04681688146936314</v>
+        <v>0.05137353971074765</v>
       </c>
       <c r="M21" t="n">
-        <v>9.645296022867541</v>
+        <v>9.672288430363999</v>
       </c>
       <c r="N21" t="n">
-        <v>176.3446176603691</v>
+        <v>176.1923403480687</v>
       </c>
       <c r="O21" t="n">
-        <v>13.27948107647167</v>
+        <v>13.27374628159167</v>
       </c>
       <c r="P21" t="n">
-        <v>325.8108576554268</v>
+        <v>325.9880833847904</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34001,28 +34237,28 @@
         <v>0.0745</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4407968893280285</v>
+        <v>-0.4350111843420298</v>
       </c>
       <c r="J22" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K22" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05528409582217353</v>
+        <v>0.05468469914439544</v>
       </c>
       <c r="M22" t="n">
-        <v>10.11982897511122</v>
+        <v>10.07256058668306</v>
       </c>
       <c r="N22" t="n">
-        <v>196.5060313287305</v>
+        <v>195.198075353499</v>
       </c>
       <c r="O22" t="n">
-        <v>14.01806089759673</v>
+        <v>13.97133047900231</v>
       </c>
       <c r="P22" t="n">
-        <v>318.2664603349108</v>
+        <v>318.2073066788836</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34079,28 +34315,28 @@
         <v>0.1041</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2768771977511841</v>
+        <v>-0.2663340149719534</v>
       </c>
       <c r="J23" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K23" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02684193563748694</v>
+        <v>0.02519470907501364</v>
       </c>
       <c r="M23" t="n">
-        <v>9.89338716370778</v>
+        <v>9.869845497698073</v>
       </c>
       <c r="N23" t="n">
-        <v>164.490857192251</v>
+        <v>163.7667109783573</v>
       </c>
       <c r="O23" t="n">
-        <v>12.82539890967338</v>
+        <v>12.79713682736718</v>
       </c>
       <c r="P23" t="n">
-        <v>309.6046505425493</v>
+        <v>309.4968649447437</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34157,28 +34393,28 @@
         <v>0.1464</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3422617153077167</v>
+        <v>-0.3307249641061973</v>
       </c>
       <c r="J24" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K24" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0609633572620073</v>
+        <v>0.05770196699863395</v>
       </c>
       <c r="M24" t="n">
-        <v>8.199943433151002</v>
+        <v>8.187962538156661</v>
       </c>
       <c r="N24" t="n">
-        <v>105.7165699894523</v>
+        <v>105.5176675015798</v>
       </c>
       <c r="O24" t="n">
-        <v>10.2818563493881</v>
+        <v>10.272179296604</v>
       </c>
       <c r="P24" t="n">
-        <v>312.2362452723233</v>
+        <v>312.117355312012</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34235,28 +34471,28 @@
         <v>0.0917</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1207423580002079</v>
+        <v>-0.1123301932102761</v>
       </c>
       <c r="J25" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K25" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01701489093991659</v>
+        <v>0.01490434798005469</v>
       </c>
       <c r="M25" t="n">
-        <v>5.509242989697511</v>
+        <v>5.504439880637643</v>
       </c>
       <c r="N25" t="n">
-        <v>49.34575862773934</v>
+        <v>49.26653199553129</v>
       </c>
       <c r="O25" t="n">
-        <v>7.024653630446084</v>
+        <v>7.019012180893498</v>
       </c>
       <c r="P25" t="n">
-        <v>310.0264623902082</v>
+        <v>309.9397552136965</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34313,28 +34549,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1015642659416837</v>
+        <v>-0.09349590759149821</v>
       </c>
       <c r="J26" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K26" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01024880687735052</v>
+        <v>0.008793724655069335</v>
       </c>
       <c r="M26" t="n">
-        <v>5.925287558657029</v>
+        <v>5.91537938422401</v>
       </c>
       <c r="N26" t="n">
-        <v>58.36430888420927</v>
+        <v>58.20629329729189</v>
       </c>
       <c r="O26" t="n">
-        <v>7.639653714940833</v>
+        <v>7.629304902629851</v>
       </c>
       <c r="P26" t="n">
-        <v>313.8321268693354</v>
+        <v>313.7489722053311</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34391,28 +34627,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1336698351586463</v>
+        <v>0.1329926787249014</v>
       </c>
       <c r="J27" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K27" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01019271967674318</v>
+        <v>0.01024773254803912</v>
       </c>
       <c r="M27" t="n">
-        <v>8.034904130528112</v>
+        <v>7.983184128312405</v>
       </c>
       <c r="N27" t="n">
-        <v>101.6576681309373</v>
+        <v>100.913147048396</v>
       </c>
       <c r="O27" t="n">
-        <v>10.08254274133947</v>
+        <v>10.04555359591476</v>
       </c>
       <c r="P27" t="n">
-        <v>317.8961426313002</v>
+        <v>317.9031043630742</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34469,28 +34705,28 @@
         <v>0.0588</v>
       </c>
       <c r="I28" t="n">
-        <v>0.04277791617377335</v>
+        <v>0.04559555203888713</v>
       </c>
       <c r="J28" t="n">
+        <v>271</v>
+      </c>
+      <c r="K28" t="n">
         <v>269</v>
       </c>
-      <c r="K28" t="n">
-        <v>267</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.0008141254726954372</v>
+        <v>0.0009392452446881361</v>
       </c>
       <c r="M28" t="n">
-        <v>9.318879737515539</v>
+        <v>9.260261224960336</v>
       </c>
       <c r="N28" t="n">
-        <v>130.0358484277286</v>
+        <v>129.1011493849921</v>
       </c>
       <c r="O28" t="n">
-        <v>11.40332620018074</v>
+        <v>11.36226867245235</v>
       </c>
       <c r="P28" t="n">
-        <v>330.2868919792601</v>
+        <v>330.2575615579633</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34547,28 +34783,28 @@
         <v>0.0577</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.03630241726163379</v>
+        <v>-0.02134385942397413</v>
       </c>
       <c r="J29" t="n">
+        <v>271</v>
+      </c>
+      <c r="K29" t="n">
         <v>269</v>
       </c>
-      <c r="K29" t="n">
-        <v>267</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.0006226537761863105</v>
+        <v>0.0002188534026608124</v>
       </c>
       <c r="M29" t="n">
-        <v>8.976038828198657</v>
+        <v>8.904213851311011</v>
       </c>
       <c r="N29" t="n">
-        <v>122.468067773995</v>
+        <v>121.4981880809401</v>
       </c>
       <c r="O29" t="n">
-        <v>11.06652916564155</v>
+        <v>11.02262165190024</v>
       </c>
       <c r="P29" t="n">
-        <v>339.6743024777201</v>
+        <v>339.5191144890833</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34625,28 +34861,28 @@
         <v>0.0459</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2192779361910435</v>
+        <v>-0.2031545651339009</v>
       </c>
       <c r="J30" t="n">
+        <v>271</v>
+      </c>
+      <c r="K30" t="n">
         <v>269</v>
       </c>
-      <c r="K30" t="n">
-        <v>267</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.02190855676281334</v>
+        <v>0.01901309819149766</v>
       </c>
       <c r="M30" t="n">
-        <v>9.018847068112782</v>
+        <v>9.021409368386129</v>
       </c>
       <c r="N30" t="n">
-        <v>124.2866445965227</v>
+        <v>124.318496014962</v>
       </c>
       <c r="O30" t="n">
-        <v>11.14839201842682</v>
+        <v>11.14982044765574</v>
       </c>
       <c r="P30" t="n">
-        <v>342.921084985612</v>
+        <v>342.7533213450197</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -34703,28 +34939,28 @@
         <v>0.0523</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3451182788520397</v>
+        <v>-0.3237197050774235</v>
       </c>
       <c r="J31" t="n">
+        <v>271</v>
+      </c>
+      <c r="K31" t="n">
         <v>269</v>
       </c>
-      <c r="K31" t="n">
-        <v>267</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.05930651262437181</v>
+        <v>0.05257341668450333</v>
       </c>
       <c r="M31" t="n">
-        <v>8.870183741680055</v>
+        <v>8.92233508335841</v>
       </c>
       <c r="N31" t="n">
-        <v>109.3831880047623</v>
+        <v>110.2528676365768</v>
       </c>
       <c r="O31" t="n">
-        <v>10.45864178585165</v>
+        <v>10.50013655323476</v>
       </c>
       <c r="P31" t="n">
-        <v>342.4675236044077</v>
+        <v>342.2448795863588</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -34781,28 +35017,28 @@
         <v>0.0591</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3804560588625311</v>
+        <v>-0.3542123145874171</v>
       </c>
       <c r="J32" t="n">
+        <v>271</v>
+      </c>
+      <c r="K32" t="n">
         <v>269</v>
       </c>
-      <c r="K32" t="n">
-        <v>267</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.06215487869781444</v>
+        <v>0.05410979831475138</v>
       </c>
       <c r="M32" t="n">
-        <v>8.592027656826227</v>
+        <v>8.666227195556493</v>
       </c>
       <c r="N32" t="n">
-        <v>126.4543614065245</v>
+        <v>128.0455179675411</v>
       </c>
       <c r="O32" t="n">
-        <v>11.24519281322132</v>
+        <v>11.31571994914778</v>
       </c>
       <c r="P32" t="n">
-        <v>347.6833119453312</v>
+        <v>347.4102558029122</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -34859,28 +35095,28 @@
         <v>0.0373</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2358760562528003</v>
+        <v>-0.2133051616832665</v>
       </c>
       <c r="J33" t="n">
+        <v>271</v>
+      </c>
+      <c r="K33" t="n">
         <v>269</v>
       </c>
-      <c r="K33" t="n">
-        <v>267</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.01460988408188169</v>
+        <v>0.01206402741752488</v>
       </c>
       <c r="M33" t="n">
-        <v>11.35141614958413</v>
+        <v>11.39032161276859</v>
       </c>
       <c r="N33" t="n">
-        <v>217.2691425257557</v>
+        <v>217.5261490704008</v>
       </c>
       <c r="O33" t="n">
-        <v>14.74005232439002</v>
+        <v>14.74876771362275</v>
       </c>
       <c r="P33" t="n">
-        <v>355.1408351053448</v>
+        <v>354.9059936286498</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -34918,7 +35154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH270"/>
+  <dimension ref="A1:AH272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80910,7 +81146,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-46.665079109684775,169.05555088650655</t>
+          <t>-46.6650385276787,169.05562091019155</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -81040,7 +81276,7 @@
       </c>
       <c r="AC270" t="inlineStr">
         <is>
-          <t>-46.661240680248056,169.0341834385116</t>
+          <t>-46.661325092620665,169.03420683843575</t>
         </is>
       </c>
       <c r="AD270" t="inlineStr">
@@ -81064,6 +81300,350 @@
         </is>
       </c>
       <c r="AH270" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>-46.66545775596558,169.05628905851216</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>-46.665011665954445,169.05566725962044</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>-46.66451242767868,169.05513716032797</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>-46.66412080537891,169.0544213648898</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>-46.663669614516586,169.05378462011043</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-46.66313488678686,169.05320966733365</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-46.662638518321515,169.05256083924854</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-46.662151921454324,169.05196505915987</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>-46.66196960005632,169.05104995630475</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>-46.661728037356056,169.05019701952665</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>-46.661522864457275,169.04926538103356</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>-46.66123961944399,169.04842171952157</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>-46.66113396210254,169.04750469401648</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>-46.66092454949141,169.0466601652149</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>-46.66073653897123,169.04580371605945</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>-46.66057701457695,169.04492430984826</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>-46.66056149919833,169.04400466489784</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>-46.66054721345642,169.04311032657358</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>-46.660393815278354,169.04220403553472</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>-46.6603546867567,169.04130366312967</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>-46.6604901966447,169.04041232919647</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>-46.660540183963505,169.03951656880412</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>-46.66060133123194,169.0386104785311</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>-46.660689669503455,169.03770768474337</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>-46.66083293436976,169.0368263401135</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>-46.66094606369623,169.03594266738776</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>-46.66116350581189,169.03507948569592</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>-46.66136915305226,169.03421905243863</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>-46.66157215582936,169.03337753296572</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>-46.66176622241563,169.0325278280853</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>-46.66202540765102,169.03170262464172</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>-46.66229313682087,169.03088103348534</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:30+00:00</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>-46.66549133333388,169.05623112147313</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>-46.66505334793166,169.0555953380733</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>-46.66451242767868,169.05513716032797</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>-46.66413857788734,169.05439069861336</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-46.66369525030726,169.05374347588153</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-46.663191160715265,169.0531391076785</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-46.662638518321515,169.05256083924854</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>-46.662151921454324,169.05196505915987</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>-46.66196960005632,169.05104995630475</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>-46.661796601018466,169.05012506399217</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>-46.66152852361139,169.0492605560248</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>-46.66127935143388,169.04839727976776</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>-46.661115412907606,169.04751502480823</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>-46.660931096244795,169.0466565189988</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>-46.66075290580067,169.04579460037863</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>-46.660596416079564,169.0449147149386</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>-46.66055891300686,169.0440051407477</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>-46.660526731160274,169.04310926602258</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>-46.66041061435092,169.04220490517912</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>-46.660375708051255,169.0413047511072</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>-46.66046423445387,169.04041098579222</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>-46.66048565439219,169.03951374781172</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>-46.66054027798692,169.0386039975063</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>-46.66065933509618,169.0377022646314</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>-46.66079676782467,169.0368192347683</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>-46.66096316709605,169.03594602736553</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>-46.661174819003996,169.03508170806373</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>-46.66137595195646,169.03422093716608</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>-46.66157692967528,169.03337940077157</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>-46.66176622241563,169.0325278280853</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>-46.66202540765102,169.03170262464172</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>-46.66229313682087,169.03088103348534</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0560/nzd0560.xlsx
+++ b/data/nzd0560/nzd0560.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH272"/>
+  <dimension ref="A1:AH274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29725,6 +29725,222 @@
         </is>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>300.23</v>
+      </c>
+      <c r="C273" t="n">
+        <v>304.58</v>
+      </c>
+      <c r="D273" t="n">
+        <v>291.95</v>
+      </c>
+      <c r="E273" t="n">
+        <v>301.79</v>
+      </c>
+      <c r="F273" t="n">
+        <v>304.8</v>
+      </c>
+      <c r="G273" t="n">
+        <v>297.2</v>
+      </c>
+      <c r="H273" t="n">
+        <v>271.87</v>
+      </c>
+      <c r="I273" t="n">
+        <v>255.68</v>
+      </c>
+      <c r="J273" t="n">
+        <v>273.61</v>
+      </c>
+      <c r="K273" t="n">
+        <v>292.84</v>
+      </c>
+      <c r="L273" t="n">
+        <v>302.72</v>
+      </c>
+      <c r="M273" t="n">
+        <v>304.08</v>
+      </c>
+      <c r="N273" t="n">
+        <v>307.09</v>
+      </c>
+      <c r="O273" t="n">
+        <v>308.31</v>
+      </c>
+      <c r="P273" t="n">
+        <v>309.55</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>314.43</v>
+      </c>
+      <c r="R273" t="n">
+        <v>330.3</v>
+      </c>
+      <c r="S273" t="n">
+        <v>322.35</v>
+      </c>
+      <c r="T273" t="n">
+        <v>305.65</v>
+      </c>
+      <c r="U273" t="n">
+        <v>297.18</v>
+      </c>
+      <c r="V273" t="n">
+        <v>299.92</v>
+      </c>
+      <c r="W273" t="n">
+        <v>295.78</v>
+      </c>
+      <c r="X273" t="n">
+        <v>298.63</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>303.88</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>305.79</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>321.94</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>334.07</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>345.01</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>348.8</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>348.46</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>355.18</v>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>297.46</v>
+      </c>
+      <c r="C274" t="n">
+        <v>304.58</v>
+      </c>
+      <c r="D274" t="n">
+        <v>291.95</v>
+      </c>
+      <c r="E274" t="n">
+        <v>296.84</v>
+      </c>
+      <c r="F274" t="n">
+        <v>298.5</v>
+      </c>
+      <c r="G274" t="n">
+        <v>297.2</v>
+      </c>
+      <c r="H274" t="n">
+        <v>271.87</v>
+      </c>
+      <c r="I274" t="n">
+        <v>255.68</v>
+      </c>
+      <c r="J274" t="n">
+        <v>273.61</v>
+      </c>
+      <c r="K274" t="n">
+        <v>288.08</v>
+      </c>
+      <c r="L274" t="n">
+        <v>301.49</v>
+      </c>
+      <c r="M274" t="n">
+        <v>300.44</v>
+      </c>
+      <c r="N274" t="n">
+        <v>300.9</v>
+      </c>
+      <c r="O274" t="n">
+        <v>304.14</v>
+      </c>
+      <c r="P274" t="n">
+        <v>302.49</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>309.93</v>
+      </c>
+      <c r="R274" t="n">
+        <v>326.71</v>
+      </c>
+      <c r="S274" t="n">
+        <v>319.07</v>
+      </c>
+      <c r="T274" t="n">
+        <v>301.19</v>
+      </c>
+      <c r="U274" t="n">
+        <v>293.1</v>
+      </c>
+      <c r="V274" t="n">
+        <v>297.26</v>
+      </c>
+      <c r="W274" t="n">
+        <v>293.31</v>
+      </c>
+      <c r="X274" t="n">
+        <v>296.66</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>299.97</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>305.79</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>326.42</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>332.65</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>349.33</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>353.27</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>350.09</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>353.74</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>349.74</v>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29736,7 +29952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B277"/>
+  <dimension ref="A1:B279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32509,6 +32725,26 @@
       </c>
       <c r="B277" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>-1.16</v>
       </c>
     </row>
   </sheetData>
@@ -32677,28 +32913,28 @@
         <v>0.1765</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6895162796801195</v>
+        <v>-0.6850447181627151</v>
       </c>
       <c r="J2" t="n">
+        <v>273</v>
+      </c>
+      <c r="K2" t="n">
         <v>271</v>
       </c>
-      <c r="K2" t="n">
-        <v>269</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2278134224582106</v>
+        <v>0.2280719422284084</v>
       </c>
       <c r="M2" t="n">
-        <v>7.625753142424597</v>
+        <v>7.590829622430515</v>
       </c>
       <c r="N2" t="n">
-        <v>95.28837508945549</v>
+        <v>94.67578433579591</v>
       </c>
       <c r="O2" t="n">
-        <v>9.761576465379733</v>
+        <v>9.730148217565645</v>
       </c>
       <c r="P2" t="n">
-        <v>314.0749064544814</v>
+        <v>314.0285960878667</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32755,28 +32991,28 @@
         <v>0.0501</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.298950538140228</v>
+        <v>-1.290627880560632</v>
       </c>
       <c r="J3" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K3" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3421014797747425</v>
+        <v>0.3423513175768227</v>
       </c>
       <c r="M3" t="n">
-        <v>10.78853442610564</v>
+        <v>10.75899553912011</v>
       </c>
       <c r="N3" t="n">
-        <v>194.001007732044</v>
+        <v>192.8441455133441</v>
       </c>
       <c r="O3" t="n">
-        <v>13.92842445260927</v>
+        <v>13.88683353084295</v>
       </c>
       <c r="P3" t="n">
-        <v>333.2932054474334</v>
+        <v>333.2077226835337</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32833,28 +33069,28 @@
         <v>0.0344</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.057804379067479</v>
+        <v>-1.06177114802661</v>
       </c>
       <c r="J4" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K4" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2601815450550254</v>
+        <v>0.2645777671985067</v>
       </c>
       <c r="M4" t="n">
-        <v>10.732437522416</v>
+        <v>10.67135377570039</v>
       </c>
       <c r="N4" t="n">
-        <v>187.4354149492804</v>
+        <v>186.106637534453</v>
       </c>
       <c r="O4" t="n">
-        <v>13.6907054219014</v>
+        <v>13.64209065848974</v>
       </c>
       <c r="P4" t="n">
-        <v>323.1884050728948</v>
+        <v>323.229576723883</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32911,28 +33147,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7284825195761964</v>
+        <v>-0.7168071950185679</v>
       </c>
       <c r="J5" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K5" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1856431900025119</v>
+        <v>0.1824835724171355</v>
       </c>
       <c r="M5" t="n">
-        <v>9.52703787639002</v>
+        <v>9.512276103699287</v>
       </c>
       <c r="N5" t="n">
-        <v>137.9637372480871</v>
+        <v>137.5183393727455</v>
       </c>
       <c r="O5" t="n">
-        <v>11.7457965778438</v>
+        <v>11.72682136696665</v>
       </c>
       <c r="P5" t="n">
-        <v>310.3093112553299</v>
+        <v>310.1886895613412</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32989,28 +33225,28 @@
         <v>0.0596</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6351029396111394</v>
+        <v>-0.6238905049179788</v>
       </c>
       <c r="J6" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K6" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1719187097514536</v>
+        <v>0.1683763769429437</v>
       </c>
       <c r="M6" t="n">
-        <v>8.831390674018934</v>
+        <v>8.818815548911932</v>
       </c>
       <c r="N6" t="n">
-        <v>115.9316187185398</v>
+        <v>115.6424871295415</v>
       </c>
       <c r="O6" t="n">
-        <v>10.76715462499447</v>
+        <v>10.75371968806801</v>
       </c>
       <c r="P6" t="n">
-        <v>310.4282411447932</v>
+        <v>310.3130986948424</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33067,28 +33303,28 @@
         <v>0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5744442859594306</v>
+        <v>-0.5617533260505243</v>
       </c>
       <c r="J7" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K7" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1512476896033659</v>
+        <v>0.1468574354020262</v>
       </c>
       <c r="M7" t="n">
-        <v>7.962822144966836</v>
+        <v>7.957622556444914</v>
       </c>
       <c r="N7" t="n">
-        <v>111.2078801538178</v>
+        <v>110.9993117443629</v>
       </c>
       <c r="O7" t="n">
-        <v>10.54551469364193</v>
+        <v>10.53562108963505</v>
       </c>
       <c r="P7" t="n">
-        <v>303.3816357995128</v>
+        <v>303.2520352373144</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33145,28 +33381,28 @@
         <v>0.0326</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7829564521176895</v>
+        <v>-0.7842033491720214</v>
       </c>
       <c r="J8" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K8" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1156429152302436</v>
+        <v>0.1175870791758657</v>
       </c>
       <c r="M8" t="n">
-        <v>13.18018788117096</v>
+        <v>13.08854122528225</v>
       </c>
       <c r="N8" t="n">
-        <v>279.3370613393631</v>
+        <v>277.2505478874186</v>
       </c>
       <c r="O8" t="n">
-        <v>16.71337971026097</v>
+        <v>16.65084225759822</v>
       </c>
       <c r="P8" t="n">
-        <v>293.7691276398393</v>
+        <v>293.7819549201691</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33223,28 +33459,28 @@
         <v>0.0309</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.323687285861321</v>
+        <v>-1.329045389942192</v>
       </c>
       <c r="J9" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K9" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1843959932297996</v>
+        <v>0.1879926334424576</v>
       </c>
       <c r="M9" t="n">
-        <v>16.52507962637361</v>
+        <v>16.42967202304514</v>
       </c>
       <c r="N9" t="n">
-        <v>446.9341312609873</v>
+        <v>443.6652626314977</v>
       </c>
       <c r="O9" t="n">
-        <v>21.14081671225091</v>
+        <v>21.06336304181974</v>
       </c>
       <c r="P9" t="n">
-        <v>294.9431585178781</v>
+        <v>294.9996531662785</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33301,28 +33537,28 @@
         <v>0.0409</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3255091830887916</v>
+        <v>-0.3388402034858127</v>
       </c>
       <c r="J10" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K10" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01552860484720719</v>
+        <v>0.01702870429859615</v>
       </c>
       <c r="M10" t="n">
-        <v>16.30223041379558</v>
+        <v>16.25816008426776</v>
       </c>
       <c r="N10" t="n">
-        <v>401.9797278560905</v>
+        <v>399.6333494664722</v>
       </c>
       <c r="O10" t="n">
-        <v>20.04943210806956</v>
+        <v>19.99083163518897</v>
       </c>
       <c r="P10" t="n">
-        <v>292.0514674388124</v>
+        <v>292.1898059528094</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33379,28 +33615,28 @@
         <v>0.0649</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.319284766179406</v>
+        <v>-1.299882385535451</v>
       </c>
       <c r="J11" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K11" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2277275484016821</v>
+        <v>0.2245944127156074</v>
       </c>
       <c r="M11" t="n">
-        <v>14.84779595101091</v>
+        <v>14.81770805256436</v>
       </c>
       <c r="N11" t="n">
-        <v>354.6248794772275</v>
+        <v>353.4449238399067</v>
       </c>
       <c r="O11" t="n">
-        <v>18.83148638523331</v>
+        <v>18.80013095273293</v>
       </c>
       <c r="P11" t="n">
-        <v>311.8673091083413</v>
+        <v>311.6699250059974</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33457,28 +33693,28 @@
         <v>0.1385</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5397808658492177</v>
+        <v>-0.536653248456523</v>
       </c>
       <c r="J12" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K12" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06747519475329378</v>
+        <v>0.06770199894259632</v>
       </c>
       <c r="M12" t="n">
-        <v>12.26883193732246</v>
+        <v>12.1918826670327</v>
       </c>
       <c r="N12" t="n">
-        <v>240.2785720464886</v>
+        <v>238.5589973184567</v>
       </c>
       <c r="O12" t="n">
-        <v>15.50092165151765</v>
+        <v>15.4453552020812</v>
       </c>
       <c r="P12" t="n">
-        <v>314.279239287217</v>
+        <v>314.2471193457078</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33535,28 +33771,28 @@
         <v>0.0963</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6674150234077891</v>
+        <v>-0.6532601021414886</v>
       </c>
       <c r="J13" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K13" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1041270112584582</v>
+        <v>0.1013237054901699</v>
       </c>
       <c r="M13" t="n">
-        <v>12.35696384639684</v>
+        <v>12.34915636274821</v>
       </c>
       <c r="N13" t="n">
-        <v>230.318912065298</v>
+        <v>229.3835003119027</v>
       </c>
       <c r="O13" t="n">
-        <v>15.17626146537078</v>
+        <v>15.14541185679355</v>
       </c>
       <c r="P13" t="n">
-        <v>309.9602644986816</v>
+        <v>309.8162747288424</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33613,28 +33849,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9973813803014879</v>
+        <v>-0.9729042605903337</v>
       </c>
       <c r="J14" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K14" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1545768113713729</v>
+        <v>0.1493048143783653</v>
       </c>
       <c r="M14" t="n">
-        <v>14.62760756923798</v>
+        <v>14.66614107246223</v>
       </c>
       <c r="N14" t="n">
-        <v>328.9158986797029</v>
+        <v>328.7702756862756</v>
       </c>
       <c r="O14" t="n">
-        <v>18.13603867110188</v>
+        <v>18.13202348570825</v>
       </c>
       <c r="P14" t="n">
-        <v>313.217412941208</v>
+        <v>312.9688029664592</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33691,28 +33927,28 @@
         <v>0.0604</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7663162393761522</v>
+        <v>-0.751929001537161</v>
       </c>
       <c r="J15" t="n">
+        <v>273</v>
+      </c>
+      <c r="K15" t="n">
         <v>271</v>
       </c>
-      <c r="K15" t="n">
-        <v>269</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1263447830641402</v>
+        <v>0.1235083601145459</v>
       </c>
       <c r="M15" t="n">
-        <v>12.52806744052877</v>
+        <v>12.50974147560268</v>
       </c>
       <c r="N15" t="n">
-        <v>244.0638178372675</v>
+        <v>243.101944301231</v>
       </c>
       <c r="O15" t="n">
-        <v>15.62254197745257</v>
+        <v>15.59172679023177</v>
       </c>
       <c r="P15" t="n">
-        <v>316.1935575743109</v>
+        <v>316.0464195298221</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33769,28 +34005,28 @@
         <v>0.0507</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6694354515787077</v>
+        <v>-0.6641601050182304</v>
       </c>
       <c r="J16" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K16" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08700157979508061</v>
+        <v>0.08691061925128252</v>
       </c>
       <c r="M16" t="n">
-        <v>13.1940455242648</v>
+        <v>13.12417732347581</v>
       </c>
       <c r="N16" t="n">
-        <v>280.6235586634397</v>
+        <v>278.7667881082265</v>
       </c>
       <c r="O16" t="n">
-        <v>16.75182254751523</v>
+        <v>16.69631061367231</v>
       </c>
       <c r="P16" t="n">
-        <v>320.0910702996455</v>
+        <v>320.0369115562996</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33847,28 +34083,28 @@
         <v>0.0455</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3999751802236621</v>
+        <v>0.3839319882973671</v>
       </c>
       <c r="J17" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K17" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02517949609776371</v>
+        <v>0.02353267640305934</v>
       </c>
       <c r="M17" t="n">
-        <v>14.06793452620234</v>
+        <v>14.0639796336859</v>
       </c>
       <c r="N17" t="n">
-        <v>369.7636830286764</v>
+        <v>368.0820096122946</v>
       </c>
       <c r="O17" t="n">
-        <v>19.2292403133529</v>
+        <v>19.18546349745803</v>
       </c>
       <c r="P17" t="n">
-        <v>313.2429730446366</v>
+        <v>313.4079537964921</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33925,28 +34161,28 @@
         <v>0.0552</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2260456617973897</v>
+        <v>0.2160461180208263</v>
       </c>
       <c r="J18" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K18" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02711272366097939</v>
+        <v>0.0251071092016748</v>
       </c>
       <c r="M18" t="n">
-        <v>8.383810770887349</v>
+        <v>8.374020043489148</v>
       </c>
       <c r="N18" t="n">
-        <v>109.6216992584623</v>
+        <v>109.2283942155316</v>
       </c>
       <c r="O18" t="n">
-        <v>10.47003816891144</v>
+        <v>10.45123888424389</v>
       </c>
       <c r="P18" t="n">
-        <v>329.800785879448</v>
+        <v>329.9035049537205</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34003,28 +34239,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0007172439740164237</v>
+        <v>-0.01141768140390829</v>
       </c>
       <c r="J19" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K19" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L19" t="n">
-        <v>2.852111821161074e-07</v>
+        <v>7.30737508999324e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>8.282767853200681</v>
+        <v>8.286909599370233</v>
       </c>
       <c r="N19" t="n">
-        <v>107.6294125047633</v>
+        <v>107.3044463132645</v>
       </c>
       <c r="O19" t="n">
-        <v>10.37445962471122</v>
+        <v>10.35878594784469</v>
       </c>
       <c r="P19" t="n">
-        <v>328.6034564816103</v>
+        <v>328.7133744765558</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34081,28 +34317,28 @@
         <v>0.0559</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2118641429073952</v>
+        <v>-0.2390173863601939</v>
       </c>
       <c r="J20" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K20" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01726832784811572</v>
+        <v>0.02179921124174355</v>
       </c>
       <c r="M20" t="n">
-        <v>9.622452058988291</v>
+        <v>9.697269180738722</v>
       </c>
       <c r="N20" t="n">
-        <v>152.4275304444855</v>
+        <v>154.2059848236348</v>
       </c>
       <c r="O20" t="n">
-        <v>12.34615448001868</v>
+        <v>12.41797023766907</v>
       </c>
       <c r="P20" t="n">
-        <v>329.0812770441402</v>
+        <v>329.360189170696</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34159,28 +34395,28 @@
         <v>0.0507</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3998837237603018</v>
+        <v>-0.4272278011649489</v>
       </c>
       <c r="J21" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K21" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05137353971074765</v>
+        <v>0.05814981272162767</v>
       </c>
       <c r="M21" t="n">
-        <v>9.672288430363999</v>
+        <v>9.754607527278761</v>
       </c>
       <c r="N21" t="n">
-        <v>176.1923403480687</v>
+        <v>177.8310260377021</v>
       </c>
       <c r="O21" t="n">
-        <v>13.27374628159167</v>
+        <v>13.33532999358104</v>
       </c>
       <c r="P21" t="n">
-        <v>325.9880833847904</v>
+        <v>326.2689542110812</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34237,28 +34473,28 @@
         <v>0.0745</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4350111843420298</v>
+        <v>-0.4458179973503473</v>
       </c>
       <c r="J22" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K22" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05468469914439544</v>
+        <v>0.05798348912421591</v>
       </c>
       <c r="M22" t="n">
-        <v>10.07256058668306</v>
+        <v>10.0623149131325</v>
       </c>
       <c r="N22" t="n">
-        <v>195.198075353499</v>
+        <v>194.2336078270047</v>
       </c>
       <c r="O22" t="n">
-        <v>13.97133047900231</v>
+        <v>13.93677178642905</v>
       </c>
       <c r="P22" t="n">
-        <v>318.2073066788836</v>
+        <v>318.3183149962116</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34315,28 +34551,28 @@
         <v>0.1041</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2663340149719534</v>
+        <v>-0.2769448369183524</v>
       </c>
       <c r="J23" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K23" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02519470907501364</v>
+        <v>0.02752291917529381</v>
       </c>
       <c r="M23" t="n">
-        <v>9.869845497698073</v>
+        <v>9.86039234774185</v>
       </c>
       <c r="N23" t="n">
-        <v>163.7667109783573</v>
+        <v>163.0145765659423</v>
       </c>
       <c r="O23" t="n">
-        <v>12.79713682736718</v>
+        <v>12.76771618442164</v>
       </c>
       <c r="P23" t="n">
-        <v>309.4968649447437</v>
+        <v>309.6058595601593</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34393,28 +34629,28 @@
         <v>0.1464</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3307249641061973</v>
+        <v>-0.3384092272553725</v>
       </c>
       <c r="J24" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K24" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L24" t="n">
-        <v>0.05770196699863395</v>
+        <v>0.06100458670561193</v>
       </c>
       <c r="M24" t="n">
-        <v>8.187962538156661</v>
+        <v>8.176409247106708</v>
       </c>
       <c r="N24" t="n">
-        <v>105.5176675015798</v>
+        <v>104.974655859097</v>
       </c>
       <c r="O24" t="n">
-        <v>10.272179296604</v>
+        <v>10.24571402387832</v>
       </c>
       <c r="P24" t="n">
-        <v>312.117355312012</v>
+        <v>312.1969212791255</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34471,28 +34707,28 @@
         <v>0.0917</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1123301932102761</v>
+        <v>-0.1191865404779798</v>
       </c>
       <c r="J25" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K25" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01490434798005469</v>
+        <v>0.01693355920889927</v>
       </c>
       <c r="M25" t="n">
-        <v>5.504439880637643</v>
+        <v>5.506908114413733</v>
       </c>
       <c r="N25" t="n">
-        <v>49.26653199553129</v>
+        <v>49.11205804386736</v>
       </c>
       <c r="O25" t="n">
-        <v>7.019012180893498</v>
+        <v>7.007999575047601</v>
       </c>
       <c r="P25" t="n">
-        <v>309.9397552136965</v>
+        <v>310.0107564286707</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34549,28 +34785,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.09349590759149821</v>
+        <v>-0.1009690348238052</v>
       </c>
       <c r="J26" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K26" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L26" t="n">
-        <v>0.008793724655069335</v>
+        <v>0.01036060761980362</v>
       </c>
       <c r="M26" t="n">
-        <v>5.91537938422401</v>
+        <v>5.919261547180118</v>
       </c>
       <c r="N26" t="n">
-        <v>58.20629329729189</v>
+        <v>57.99188729183297</v>
       </c>
       <c r="O26" t="n">
-        <v>7.629304902629851</v>
+        <v>7.615240461852336</v>
       </c>
       <c r="P26" t="n">
-        <v>313.7489722053311</v>
+        <v>313.8263450411956</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34627,28 +34863,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1329926787249014</v>
+        <v>0.1367107846906296</v>
       </c>
       <c r="J27" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K27" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01024773254803912</v>
+        <v>0.01097940867480751</v>
       </c>
       <c r="M27" t="n">
-        <v>7.983184128312405</v>
+        <v>7.940066110038254</v>
       </c>
       <c r="N27" t="n">
-        <v>100.913147048396</v>
+        <v>100.2607665082181</v>
       </c>
       <c r="O27" t="n">
-        <v>10.04555359591476</v>
+        <v>10.01302983657884</v>
       </c>
       <c r="P27" t="n">
-        <v>317.9031043630742</v>
+        <v>317.864592806792</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34705,28 +34941,28 @@
         <v>0.0588</v>
       </c>
       <c r="I28" t="n">
-        <v>0.04559555203888713</v>
+        <v>0.04819504561876134</v>
       </c>
       <c r="J28" t="n">
+        <v>273</v>
+      </c>
+      <c r="K28" t="n">
         <v>271</v>
       </c>
-      <c r="K28" t="n">
-        <v>269</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.0009392452446881361</v>
+        <v>0.001065441469589312</v>
       </c>
       <c r="M28" t="n">
-        <v>9.260261224960336</v>
+        <v>9.201607730329398</v>
       </c>
       <c r="N28" t="n">
-        <v>129.1011493849921</v>
+        <v>128.1775286628209</v>
       </c>
       <c r="O28" t="n">
-        <v>11.36226867245235</v>
+        <v>11.32155151305778</v>
       </c>
       <c r="P28" t="n">
-        <v>330.2575615579633</v>
+        <v>330.230411800437</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34783,28 +35019,28 @@
         <v>0.0577</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.02134385942397413</v>
+        <v>-0.009953805427080567</v>
       </c>
       <c r="J29" t="n">
+        <v>273</v>
+      </c>
+      <c r="K29" t="n">
         <v>271</v>
       </c>
-      <c r="K29" t="n">
-        <v>269</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.0002188534026608124</v>
+        <v>4.814245243056625e-05</v>
       </c>
       <c r="M29" t="n">
-        <v>8.904213851311011</v>
+        <v>8.88623759245313</v>
       </c>
       <c r="N29" t="n">
-        <v>121.4981880809401</v>
+        <v>121.123618545856</v>
       </c>
       <c r="O29" t="n">
-        <v>11.02262165190024</v>
+        <v>11.00561759038792</v>
       </c>
       <c r="P29" t="n">
-        <v>339.5191144890833</v>
+        <v>339.4001153410986</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34861,28 +35097,28 @@
         <v>0.0459</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2031545651339009</v>
+        <v>-0.1841336847144812</v>
       </c>
       <c r="J30" t="n">
+        <v>273</v>
+      </c>
+      <c r="K30" t="n">
         <v>271</v>
       </c>
-      <c r="K30" t="n">
-        <v>269</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.01901309819149766</v>
+        <v>0.01573869956104601</v>
       </c>
       <c r="M30" t="n">
-        <v>9.021409368386129</v>
+        <v>9.0386004951364</v>
       </c>
       <c r="N30" t="n">
-        <v>124.318496014962</v>
+        <v>124.7980253237651</v>
       </c>
       <c r="O30" t="n">
-        <v>11.14982044765574</v>
+        <v>11.17130365372659</v>
       </c>
       <c r="P30" t="n">
-        <v>342.7533213450197</v>
+        <v>342.5546081476751</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -34939,28 +35175,28 @@
         <v>0.0523</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3237197050774235</v>
+        <v>-0.3019569462101571</v>
       </c>
       <c r="J31" t="n">
+        <v>273</v>
+      </c>
+      <c r="K31" t="n">
         <v>271</v>
       </c>
-      <c r="K31" t="n">
-        <v>269</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.05257341668450333</v>
+        <v>0.04602806325254116</v>
       </c>
       <c r="M31" t="n">
-        <v>8.92233508335841</v>
+        <v>8.976282076581773</v>
       </c>
       <c r="N31" t="n">
-        <v>110.2528676365768</v>
+        <v>111.2250496089435</v>
       </c>
       <c r="O31" t="n">
-        <v>10.50013655323476</v>
+        <v>10.54632872657322</v>
       </c>
       <c r="P31" t="n">
-        <v>342.2448795863588</v>
+        <v>342.0175344217673</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -35017,28 +35253,28 @@
         <v>0.0591</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3542123145874171</v>
+        <v>-0.3305990950940649</v>
       </c>
       <c r="J32" t="n">
+        <v>273</v>
+      </c>
+      <c r="K32" t="n">
         <v>271</v>
       </c>
-      <c r="K32" t="n">
-        <v>269</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.05410979831475138</v>
+        <v>0.0474253557556007</v>
       </c>
       <c r="M32" t="n">
-        <v>8.666227195556493</v>
+        <v>8.730562077003984</v>
       </c>
       <c r="N32" t="n">
-        <v>128.0455179675411</v>
+        <v>129.2085943795542</v>
       </c>
       <c r="O32" t="n">
-        <v>11.31571994914778</v>
+        <v>11.36699583793159</v>
       </c>
       <c r="P32" t="n">
-        <v>347.4102558029122</v>
+        <v>347.1635951323227</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -35095,28 +35331,28 @@
         <v>0.0373</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2133051616832665</v>
+        <v>-0.2087735627613855</v>
       </c>
       <c r="J33" t="n">
+        <v>273</v>
+      </c>
+      <c r="K33" t="n">
         <v>271</v>
       </c>
-      <c r="K33" t="n">
-        <v>269</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.01206402741752488</v>
+        <v>0.01173450289457056</v>
       </c>
       <c r="M33" t="n">
-        <v>11.39032161276859</v>
+        <v>11.33076858455542</v>
       </c>
       <c r="N33" t="n">
-        <v>217.5261490704008</v>
+        <v>216.0526528039113</v>
       </c>
       <c r="O33" t="n">
-        <v>14.74876771362275</v>
+        <v>14.69872963231555</v>
       </c>
       <c r="P33" t="n">
-        <v>354.9059936286498</v>
+        <v>354.8586753079023</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -35154,7 +35390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH272"/>
+  <dimension ref="A1:AH274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81649,6 +81885,350 @@
         </is>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>-46.66548172326277,169.05624770346054</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>-46.66504941130258,169.05560213066858</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>-46.66451879573024,169.05512617238898</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>-46.66411825817827,169.0544257600548</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>-46.66367070026805,169.05378287753211</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>-46.663171495466486,169.05316376518059</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>-46.662625402846224,169.05257460316454</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>-46.66216401679522,169.05195236580892</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>-46.66195123857377,169.05106922587083</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>-46.66174792883834,169.05017614402934</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>-46.66146177658668,169.04931746462398</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>-46.66121809794674,169.04843495770592</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>-46.66103945352213,169.0475573295567</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>-46.6608490939512,169.0467021901258</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>-46.66065890143425,169.04584695703068</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>-46.66049719610324,169.0449637835666</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>-46.660478919427426,169.0440198592501</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>-46.66045252775369,169.04310542385343</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>-46.66034566392584,169.04220154286523</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>-46.66031273400203,169.0413014918251</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>-46.66038050863389,169.04040665343294</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>-46.66038647704917,169.03950861705005</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>-46.660456453046315,169.0385950991995</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>-46.66059447299529,169.03769067517348</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>-46.660715704877575,169.03680330902347</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>-46.66096316709605,169.03594602736553</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>-46.661174819003996,169.03508170806373</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>-46.66137595195646,169.03422093716608</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>-46.66157692967528,169.03337940077157</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>-46.66176622241563,169.0325278280853</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>-46.66202540765102,169.03170262464172</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>-46.6622093326585,169.0308455918329</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>-46.665465687174425,169.0562753733904</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>-46.66504941130258,169.05560213066858</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>-46.66451879573024,169.05512617238898</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>-46.66408960215853,169.05447520563294</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>-46.6636326989497,169.0538438677319</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>-46.663171495466486,169.05316376518059</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>-46.662625402846224,169.05257460316454</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>-46.66216401679522,169.05195236580892</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>-46.66195123857377,169.05106922587083</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>-46.66171324625101,169.05021254232227</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>-46.661452241294704,169.04932559441212</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>-46.66118796784733,169.04845349114555</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>-46.66098749896956,169.0475862649979</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>-46.66081409398866,169.04672168328523</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>-46.66059964509461,169.0458799603222</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>-46.66045890365208,169.04498272080775</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>-46.66044690415871,169.04402574991846</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>-46.66042306199403,169.04310389815058</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>-46.660305597688314,169.04219946874224</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>-46.66027608148819,169.04129959484052</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>-46.66035661263794,169.04040541694505</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>-46.66036428791524,169.03950746913605</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>-46.660438791534666,169.0385932243715</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>-46.66055958842623,169.03768444206318</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>-46.660715704877575,169.03680330902347</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>-46.66100307502871,169.03595386732067</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>-46.661162169608104,169.0350792232116</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>-46.66141409645746,169.03423151122925</t>
+        </is>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>-46.66161572802221,169.0333945809504</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>-46.6617802904214,169.03253377786584</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>-46.66200434876126,169.0316937184118</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>-46.66216238161012,169.03082573579212</t>
+        </is>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
